--- a/data/seed/portfolio/L-2025-5531/vypiska_2026-07_09.xlsx
+++ b/data/seed/portfolio/L-2025-5531/vypiska_2026-07_09.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J146"/>
+  <dimension ref="A1:J180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -540,37 +540,37 @@
       <c r="B8" t="n">
         <v>100</v>
       </c>
-      <c r="C8" s="2" t="n"/>
-      <c r="D8" s="2" t="n">
-        <v>7512000</v>
-      </c>
+      <c r="C8" s="2" t="n">
+        <v>59978000</v>
+      </c>
+      <c r="D8" s="2" t="n"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Jizzax Yog'och MChJ</t>
+          <t>Lazzat Oziq-ovqat Savdo AJ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>362365657</t>
+          <t>331053414</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>20208000386072293001</t>
+          <t>20208000402896757001</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №6483 01.07.2026, QQS bilan</t>
+          <t>Предоплата за материалы по договору №161/26</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>183612000</v>
+        <v>116122000</v>
       </c>
     </row>
     <row r="9">
@@ -581,142 +581,142 @@
         <v>101</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>145823000</v>
+        <v>8063000</v>
       </c>
       <c r="D9" s="2" t="n"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Nukus Poligraf AJ</t>
+          <t>Nukus Mebel MChJ</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>217953808</t>
+          <t>328573767</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>20208000462352734001</t>
+          <t>20208000514928282001</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>TRANSPORT XIZMATLARI UCHUN TO'LOV, SHARTNOMA №202/26</t>
+          <t>Оплата за транспортные услуги по дог. №4/26</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>37789000</v>
+        <v>108059000</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>46209</v>
+        <v>46206</v>
       </c>
       <c r="B10" t="n">
         <v>102</v>
       </c>
       <c r="C10" s="2" t="n"/>
       <c r="D10" s="2" t="n">
-        <v>65144000</v>
+        <v>20853000</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Nurafshon Metall MChJ</t>
+          <t>Zarafshon Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>325368505</t>
+          <t>336850572</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20208000246078378001</t>
+          <t>20208000607837882001</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №5677 06.07.2026, QQS bilan</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №4768</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>102933000</v>
+        <v>128912000</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>46209</v>
+        <v>46206</v>
       </c>
       <c r="B11" t="n">
         <v>103</v>
       </c>
       <c r="C11" s="2" t="n"/>
       <c r="D11" s="2" t="n">
-        <v>23711000</v>
+        <v>13803000</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Nurafshon Metall MChJ</t>
+          <t>Saodat Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>325368505</t>
+          <t>256884648</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20208000246078378001</t>
+          <t>20208000716469607001</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisb-faktura №2021 06.07.2026, QQS bilan</t>
+          <t>Оплата за продукцию по договору №64/26, НДС 12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>126644000</v>
+        <v>142715000</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>46209</v>
+        <v>46206</v>
       </c>
       <c r="B12" t="n">
         <v>104</v>
       </c>
       <c r="C12" s="2" t="n"/>
       <c r="D12" s="2" t="n">
-        <v>21802000</v>
+        <v>4276000</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bahor Yog' Zavodi MChJ</t>
+          <t>Zarafshon Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>330568846</t>
+          <t>336850572</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20208000807164696001</t>
+          <t>20208000607837882001</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -726,11 +726,11 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №9923 06.07.2026, QQS bilan</t>
+          <t>Оплата за продукцию по дог. №69/26, НДС 12%</t>
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>148446000</v>
+        <v>146991000</v>
       </c>
     </row>
     <row r="13">
@@ -742,35 +742,35 @@
       </c>
       <c r="C13" s="2" t="n"/>
       <c r="D13" s="2" t="n">
-        <v>12696000</v>
+        <v>60491000</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Chirchiq Mato XK</t>
+          <t>Kattaqo'rg'on Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>245637587</t>
+          <t>348349936</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20208000286988280001</t>
+          <t>20208000263627433001</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №132/26, QQS 12%</t>
+          <t>Предоплата за товар по договору №207/26 от 06.07.2026</t>
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>161142000</v>
+        <v>207482000</v>
       </c>
     </row>
     <row r="14">
@@ -782,35 +782,35 @@
       </c>
       <c r="C14" s="2" t="n"/>
       <c r="D14" s="2" t="n">
-        <v>11492000</v>
+        <v>10113000</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Nihol Sut Mahsulotlari MChJ</t>
+          <t>Zarafshon Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>308432682</t>
+          <t>336850572</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20208000052496380001</t>
+          <t>20208000607837882001</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №1354 от 06.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №3608 от 06.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>172634000</v>
+        <v>217595000</v>
       </c>
     </row>
     <row r="15">
@@ -820,23 +820,23 @@
       <c r="B15" t="n">
         <v>107</v>
       </c>
-      <c r="C15" s="2" t="n">
-        <v>4846000</v>
-      </c>
-      <c r="D15" s="2" t="n"/>
+      <c r="C15" s="2" t="n"/>
+      <c r="D15" s="2" t="n">
+        <v>6495000</v>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Nukus Poligraf AJ</t>
+          <t>Zarafshon Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>217953808</t>
+          <t>336850572</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>20208000462352734001</t>
+          <t>20208000607837882001</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -846,11 +846,11 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartn. №112/26, QQS bilan</t>
+          <t>Предоплата за товар по договору №173/26 от 06.07.2026</t>
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>167788000</v>
+        <v>224090000</v>
       </c>
     </row>
     <row r="16">
@@ -860,37 +860,37 @@
       <c r="B16" t="n">
         <v>108</v>
       </c>
-      <c r="C16" s="2" t="n">
-        <v>5811000</v>
-      </c>
-      <c r="D16" s="2" t="n"/>
+      <c r="C16" s="2" t="n"/>
+      <c r="D16" s="2" t="n">
+        <v>5331000</v>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Oqtosh Agro Servis XK</t>
+          <t>Zarafshon Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>225285737</t>
+          <t>336850572</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>20208000715149282001</t>
+          <t>20208000607837882001</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №209/26</t>
+          <t>Оплата за товар по счет-фактуре №5880 от 06.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>161977000</v>
+        <v>229421000</v>
       </c>
     </row>
     <row r="17">
@@ -900,37 +900,37 @@
       <c r="B17" t="n">
         <v>109</v>
       </c>
-      <c r="C17" s="2" t="n">
-        <v>9118000</v>
-      </c>
-      <c r="D17" s="2" t="n"/>
+      <c r="C17" s="2" t="n"/>
+      <c r="D17" s="2" t="n">
+        <v>3484000</v>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Mehnat Polimer MChJ</t>
+          <t>Zarafshon Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>267270449</t>
+          <t>336850572</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20208000582882038001</t>
+          <t>20208000607837882001</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №5142</t>
+          <t>Оплата за продукцию по договору №37/26, НДС 12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>152859000</v>
+        <v>232905000</v>
       </c>
     </row>
     <row r="18">
@@ -940,338 +940,338 @@
       <c r="B18" t="n">
         <v>110</v>
       </c>
-      <c r="C18" s="2" t="n">
-        <v>20420000</v>
-      </c>
-      <c r="D18" s="2" t="n"/>
+      <c r="C18" s="2" t="n"/>
+      <c r="D18" s="2" t="n">
+        <v>3075000</v>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sarbon Moliya Bank</t>
+          <t>Zarafshon Avto Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>336850572</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000607837882001</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Заработная плата за июнь 2026 г. (перечисление на пластиковые карты)</t>
+          <t>Оплата по счет-фактуре №1623 за поставленный товар</t>
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>132439000</v>
+        <v>235980000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>46210</v>
+        <v>46209</v>
       </c>
       <c r="B19" t="n">
         <v>111</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>3563000</v>
+        <v>15251000</v>
       </c>
       <c r="D19" s="2" t="n"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Olmaliq Qurilish MChJ</t>
+          <t>Mehnat Non MChJ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>359731053</t>
+          <t>267657283</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20208000149402896001</t>
+          <t>20208000254733554001</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>АРЕНДА ПОМЕЩЕНИЯ ЗА ИЮЛЬ, ДОГ. №44/21</t>
+          <t>Оплата за упаковочные материалы, с/ф №3463</t>
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>128876000</v>
+        <v>220729000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>46211</v>
+        <v>46209</v>
       </c>
       <c r="B20" t="n">
         <v>112</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>24188000</v>
+        <v>20420000</v>
       </c>
       <c r="D20" s="2" t="n"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Oqtosh Agro Servis XK</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>225285737</t>
+          <t>Sarbon Moliya Bank</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>20208000715149282001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartn. №292/26</t>
+          <t>Перечисление заработной платы за июнь 2026 г. согласно реестру №8979</t>
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>104688000</v>
+        <v>200309000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>46212</v>
+        <v>46209</v>
       </c>
       <c r="B21" t="n">
         <v>113</v>
       </c>
-      <c r="C21" s="2" t="n"/>
-      <c r="D21" s="2" t="n">
-        <v>68974000</v>
-      </c>
+      <c r="C21" s="2" t="n">
+        <v>26134000</v>
+      </c>
+      <c r="D21" s="2" t="n"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Nurafshon Metall MChJ</t>
+          <t>Mehnat Non MChJ</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>325368505</t>
+          <t>267657283</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20208000246078378001</t>
+          <t>20208000254733554001</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Shartnoma №173/26 bo'yicha oldindan to'lov</t>
+          <t>Tovarlar uchun to'lov h/f №1088</t>
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>173662000</v>
+        <v>174175000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>46216</v>
+        <v>46210</v>
       </c>
       <c r="B22" t="n">
         <v>114</v>
       </c>
-      <c r="C22" s="2" t="n"/>
-      <c r="D22" s="2" t="n">
-        <v>43155000</v>
-      </c>
+      <c r="C22" s="2" t="n">
+        <v>3563000</v>
+      </c>
+      <c r="D22" s="2" t="n"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Nurafshon Metall MChJ</t>
+          <t>Durdona Qurilish MChJ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>325368505</t>
+          <t>312569656</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>20208000246078378001</t>
+          <t>20208000417219297001</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Shartnoma №50/26 bo'yicha oldindan to'lov</t>
+          <t>Bino ijarasi uchun to'lov iyul</t>
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>216817000</v>
+        <v>170612000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>46216</v>
+        <v>46211</v>
       </c>
       <c r="B23" t="n">
         <v>115</v>
       </c>
       <c r="C23" s="2" t="n"/>
       <c r="D23" s="2" t="n">
-        <v>14246000</v>
+        <v>18320000</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Nurafshon Metall MChJ</t>
+          <t>Chust Mebel MChJ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>325368505</t>
+          <t>395380844</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20208000246078378001</t>
+          <t>20208000235273440001</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №5023</t>
+          <t>Предоплата за товар по договору №168/26 от 08.07.2026</t>
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>231063000</v>
+        <v>188932000</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>46216</v>
+        <v>46212</v>
       </c>
       <c r="B24" t="n">
         <v>116</v>
       </c>
-      <c r="C24" s="2" t="n">
-        <v>5677000</v>
-      </c>
-      <c r="D24" s="2" t="n"/>
+      <c r="C24" s="2" t="n"/>
+      <c r="D24" s="2" t="n">
+        <v>4009000</v>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Meva Eksport MChJ</t>
+          <t>Saodat Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>282116549</t>
+          <t>256884648</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>20208000195837259001</t>
+          <t>20208000716469607001</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №63/26</t>
+          <t>Mahsulot uchun to'lov, shartnoma №146/26, QQS 12%</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>225386000</v>
+        <v>192941000</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>46216</v>
+        <v>46213</v>
       </c>
       <c r="B25" t="n">
         <v>117</v>
       </c>
-      <c r="C25" s="2" t="n">
-        <v>15542000</v>
-      </c>
-      <c r="D25" s="2" t="n"/>
+      <c r="C25" s="2" t="n"/>
+      <c r="D25" s="2" t="n">
+        <v>16579000</v>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Mehnat Polimer MChJ</t>
+          <t>Zarafshon Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>267270449</t>
+          <t>336850572</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>20208000582882038001</t>
+          <t>20208000607837882001</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №270/26</t>
+          <t>Mahsulot uchun to'lov, shartnoma №210/26, QQS 12%</t>
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>209844000</v>
+        <v>209520000</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>46216</v>
+        <v>46213</v>
       </c>
       <c r="B26" t="n">
         <v>118</v>
       </c>
-      <c r="C26" s="2" t="n">
-        <v>16793000</v>
-      </c>
-      <c r="D26" s="2" t="n"/>
+      <c r="C26" s="2" t="n"/>
+      <c r="D26" s="2" t="n">
+        <v>4711000</v>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Oqtosh Agro Servis XK</t>
+          <t>Lazzat Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>225285737</t>
+          <t>236565783</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>20208000715149282001</t>
+          <t>20208000607229325001</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1281,77 +1281,77 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №161/26</t>
+          <t>Оплата за продукцию по договору №217/26, НДС 12%</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>193051000</v>
+        <v>214231000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>46217</v>
+        <v>46213</v>
       </c>
       <c r="B27" t="n">
         <v>119</v>
       </c>
-      <c r="C27" s="2" t="n"/>
-      <c r="D27" s="2" t="n">
-        <v>14073000</v>
-      </c>
+      <c r="C27" s="2" t="n">
+        <v>35041000</v>
+      </c>
+      <c r="D27" s="2" t="n"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Farovon Polimer MChJ</t>
+          <t>Mehnat Non MChJ</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>245566043</t>
+          <t>267657283</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>20208000185731553001</t>
+          <t>20208000254733554001</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №6774 14.07.2026, QQS bilan</t>
+          <t>Оплата за товары согласно счет-фактуре №453</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>207124000</v>
+        <v>179190000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>46217</v>
+        <v>46216</v>
       </c>
       <c r="B28" t="n">
         <v>120</v>
       </c>
       <c r="C28" s="2" t="n"/>
       <c r="D28" s="2" t="n">
-        <v>6843000</v>
+        <v>70435000</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bahor Yog' Zavodi MChJ</t>
+          <t>Zarafshon Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>330568846</t>
+          <t>336850572</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>20208000807164696001</t>
+          <t>20208000607837882001</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1361,1742 +1361,1747 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №75/26, QQS 12%</t>
+          <t>Оплата за продукцию по договору №244/26, НДС 12%</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>213967000</v>
+        <v>249625000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>46217</v>
+        <v>46216</v>
       </c>
       <c r="B29" t="n">
         <v>121</v>
       </c>
-      <c r="C29" s="2" t="n">
-        <v>2784000</v>
-      </c>
-      <c r="D29" s="2" t="n"/>
+      <c r="C29" s="2" t="n"/>
+      <c r="D29" s="2" t="n">
+        <v>9595000</v>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Zarafshon Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>336850572</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000607837882001</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Ijtimoiy soliq iyun 2026</t>
+          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №5112 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>211183000</v>
+        <v>259220000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>46217</v>
+        <v>46216</v>
       </c>
       <c r="B30" t="n">
         <v>122</v>
       </c>
-      <c r="C30" s="2" t="n">
-        <v>2784000</v>
-      </c>
-      <c r="D30" s="2" t="n"/>
+      <c r="C30" s="2" t="n"/>
+      <c r="D30" s="2" t="n">
+        <v>6835000</v>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Zarafshon Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>336850572</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000607837882001</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Jismoniy shaxslar daromad solig'i iyun 2026</t>
+          <t>Оплата за продукцию по договору №299/26, НДС 12%</t>
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>208399000</v>
+        <v>266055000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>46218</v>
+        <v>46216</v>
       </c>
       <c r="B31" t="n">
         <v>123</v>
       </c>
       <c r="C31" s="2" t="n"/>
       <c r="D31" s="2" t="n">
-        <v>9218000</v>
+        <v>5091000</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Nurafshon Metall MChJ</t>
+          <t>Zarafshon Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>325368505</t>
+          <t>336850572</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>20208000246078378001</t>
+          <t>20208000607837882001</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Shartnoma №281/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за продукцию по договору №76/26, НДС 12%</t>
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>217617000</v>
+        <v>271146000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>46218</v>
+        <v>46216</v>
       </c>
       <c r="B32" t="n">
         <v>124</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>4502000</v>
+        <v>16246000</v>
       </c>
       <c r="D32" s="2" t="n"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Mehnat Polimer MChJ</t>
+          <t>Mehnat Non MChJ</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>267270449</t>
+          <t>267657283</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>20208000582882038001</t>
+          <t>20208000254733554001</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Transport xizmatlri uchun to'lov, shartnoma №273/26</t>
+          <t>Предоплата за материалы по договору №112/26</t>
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>213115000</v>
+        <v>254900000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>46219</v>
+        <v>46216</v>
       </c>
       <c r="B33" t="n">
         <v>125</v>
       </c>
-      <c r="C33" s="2" t="n"/>
-      <c r="D33" s="2" t="n">
-        <v>10158000</v>
-      </c>
+      <c r="C33" s="2" t="n">
+        <v>37861000</v>
+      </c>
+      <c r="D33" s="2" t="n"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Nurafshon Metall MChJ</t>
+          <t>Mehnat Non MChJ</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>325368505</t>
+          <t>267657283</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>20208000246078378001</t>
+          <t>20208000254733554001</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №2140</t>
+          <t>Оплта за транспортные услуги по договору №212/26</t>
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>223273000</v>
+        <v>217039000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
-        <v>46219</v>
+        <v>46216</v>
       </c>
       <c r="B34" t="n">
         <v>126</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>4698000</v>
+        <v>45445000</v>
       </c>
       <c r="D34" s="2" t="n"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Mehnat Polimer MChJ</t>
+          <t>Mehnat Non MChJ</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>267270449</t>
+          <t>267657283</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>20208000582882038001</t>
+          <t>20208000254733554001</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>MATERIALLAR UCHUN OLDINDAN TO'LOV, SHARTNOMA №168/26</t>
+          <t>Оплата за упаковочные материалы, с/ф №3123</t>
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>218575000</v>
+        <v>171594000</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>46220</v>
+        <v>46217</v>
       </c>
       <c r="B35" t="n">
         <v>127</v>
       </c>
-      <c r="C35" s="2" t="n">
-        <v>68666000</v>
-      </c>
-      <c r="D35" s="2" t="n"/>
+      <c r="C35" s="2" t="n"/>
+      <c r="D35" s="2" t="n">
+        <v>34406000</v>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Farovon Metall Servis MChJ</t>
+          <t>Zarafshon Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>252676572</t>
+          <t>336850572</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>20208000362547335001</t>
+          <t>20208000607837882001</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartn. №63/26, QQS bilan</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №4392</t>
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>149909000</v>
+        <v>206000000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>46223</v>
+        <v>46217</v>
       </c>
       <c r="B36" t="n">
         <v>128</v>
       </c>
       <c r="C36" s="2" t="n"/>
       <c r="D36" s="2" t="n">
-        <v>18234000</v>
+        <v>5798000</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Nurafshon Metall MChJ</t>
+          <t>Saodat Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>325368505</t>
+          <t>256884648</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>20208000246078378001</t>
+          <t>20208000716469607001</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №9373 от 20.07.2026, в т.ч. НДС 12%</t>
+          <t>Tovar uchun to'lov, h/f №1883 14.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>168143000</v>
+        <v>211798000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>46223</v>
+        <v>46217</v>
       </c>
       <c r="B37" t="n">
         <v>129</v>
       </c>
-      <c r="C37" s="2" t="n"/>
-      <c r="D37" s="2" t="n">
-        <v>10082000</v>
-      </c>
+      <c r="C37" s="2" t="n">
+        <v>2784000</v>
+      </c>
+      <c r="D37" s="2" t="n"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bahor Yog' Zavodi MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>330568846</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>20208000807164696001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №273/26, QQS 12%</t>
+          <t>Уплата социального налога за июнь</t>
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>178225000</v>
+        <v>209014000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
-        <v>46223</v>
+        <v>46217</v>
       </c>
       <c r="B38" t="n">
         <v>130</v>
       </c>
       <c r="C38" s="2" t="n">
-        <v>33500000</v>
+        <v>2784000</v>
       </c>
       <c r="D38" s="2" t="n"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-5531)</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>16307000202482792417</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-5531 bo'yicha navbatdagi to'lov (07.2026)</t>
+          <t>Налог на доходы физических лиц за июнь 2026 г.</t>
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>144725000</v>
+        <v>206230000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>46223</v>
+        <v>46217</v>
       </c>
       <c r="B39" t="n">
         <v>131</v>
       </c>
       <c r="C39" s="2" t="n">
-        <v>66238000</v>
+        <v>10529000</v>
       </c>
       <c r="D39" s="2" t="n"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Mehnat Polimer MChJ</t>
+          <t>Tong Savdo AJ</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>267270449</t>
+          <t>281252850</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>20208000582882038001</t>
+          <t>20208000537007953001</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №5596</t>
+          <t>Оплата за транспортные услуги по договору №68/26</t>
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>78487000</v>
+        <v>195701000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
-        <v>46224</v>
+        <v>46218</v>
       </c>
       <c r="B40" t="n">
         <v>132</v>
       </c>
-      <c r="C40" s="2" t="n"/>
-      <c r="D40" s="2" t="n">
-        <v>14003000</v>
-      </c>
+      <c r="C40" s="2" t="n">
+        <v>11789000</v>
+      </c>
+      <c r="D40" s="2" t="n"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Nurafshon Metall MChJ</t>
+          <t>Mehnat Non MChJ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>325368505</t>
+          <t>267657283</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>20208000246078378001</t>
+          <t>20208000254733554001</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>SHARTNOMA №268/26 BO'YICHA OLDINDAN TO'LOV</t>
+          <t>Оплата за сырье по договору №8/26 от 15.07.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>92490000</v>
+        <v>183912000</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>46224</v>
+        <v>46219</v>
       </c>
       <c r="B41" t="n">
         <v>133</v>
       </c>
       <c r="C41" s="2" t="n"/>
       <c r="D41" s="2" t="n">
-        <v>9438000</v>
+        <v>9602000</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Nurafshon Metall MChJ</t>
+          <t>Saodat Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>325368505</t>
+          <t>256884648</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>20208000246078378001</t>
+          <t>20208000716469607001</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №6/26, QQS 12%</t>
+          <t>Предоплата за товар по дог. №95/26 от 16.07.2026</t>
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>101928000</v>
+        <v>193514000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
-        <v>46224</v>
+        <v>46219</v>
       </c>
       <c r="B42" t="n">
         <v>134</v>
       </c>
-      <c r="C42" s="2" t="n">
-        <v>15745000</v>
-      </c>
-      <c r="D42" s="2" t="n"/>
+      <c r="C42" s="2" t="n"/>
+      <c r="D42" s="2" t="n">
+        <v>4378000</v>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Mehnat Polimer MChJ</t>
+          <t>Zarafshon Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>267270449</t>
+          <t>336850572</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>20208000582882038001</t>
+          <t>20208000607837882001</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №105/26, QQS bilan</t>
+          <t>Оплата за продукцию по договору №184/26, НДС 12%</t>
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>86183000</v>
+        <v>197892000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
-        <v>46225</v>
+        <v>46220</v>
       </c>
       <c r="B43" t="n">
         <v>135</v>
       </c>
       <c r="C43" s="2" t="n"/>
       <c r="D43" s="2" t="n">
-        <v>12521000</v>
+        <v>5808000</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Nurafshon Metall MChJ</t>
+          <t>Zarafshon Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>325368505</t>
+          <t>336850572</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>20208000246078378001</t>
+          <t>20208000607837882001</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №294/26, QQS 12%</t>
+          <t>Shartnoma №80/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>98704000</v>
+        <v>203700000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
-        <v>46225</v>
+        <v>46223</v>
       </c>
       <c r="B44" t="n">
         <v>136</v>
       </c>
-      <c r="C44" s="2" t="n">
-        <v>5826000</v>
-      </c>
-      <c r="D44" s="2" t="n"/>
+      <c r="C44" s="2" t="n"/>
+      <c r="D44" s="2" t="n">
+        <v>6608000</v>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Zarafshon Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>336850572</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000607837882001</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>QQS iyu 2026 uchun</t>
+          <t>Оплата за товар по с/ф №3808 от 20.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>92878000</v>
+        <v>210308000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
-        <v>46225</v>
+        <v>46223</v>
       </c>
       <c r="B45" t="n">
         <v>137</v>
       </c>
       <c r="C45" s="2" t="n">
-        <v>7053000</v>
+        <v>8661000</v>
       </c>
       <c r="D45" s="2" t="n"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Meva Eksport MChJ</t>
+          <t>Lazzat Oziq-ovqat Savdo AJ</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>282116549</t>
+          <t>331053414</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>20208000195837259001</t>
+          <t>20208000402896757001</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №8151</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №70/26</t>
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>85825000</v>
+        <v>201647000</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
-        <v>46226</v>
+        <v>46223</v>
       </c>
       <c r="B46" t="n">
         <v>138</v>
       </c>
       <c r="C46" s="2" t="n">
-        <v>6978000</v>
+        <v>33500000</v>
       </c>
       <c r="D46" s="2" t="n"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Meva Eksport MChJ</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>282116549</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-5531)</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>20208000195837259001</t>
+          <t>16307000202482792417</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №249/26, QQS bilan</t>
+          <t>Kredit shartnomasi L-2025-5531 bo'yicha navbatdagi to'lov (07.2026)</t>
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>78847000</v>
+        <v>168147000</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
-        <v>46227</v>
+        <v>46224</v>
       </c>
       <c r="B47" t="n">
         <v>139</v>
       </c>
       <c r="C47" s="2" t="n">
-        <v>8552000</v>
+        <v>12403000</v>
       </c>
       <c r="D47" s="2" t="n"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Mehnat Polimer MChJ</t>
+          <t>Mehnat Non MChJ</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>267270449</t>
+          <t>267657283</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>20208000582882038001</t>
+          <t>20208000254733554001</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartn. №248/26</t>
+          <t>Оплата за сырье по договору №139/26 от 21.07.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>70295000</v>
+        <v>155744000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
-        <v>46230</v>
+        <v>46225</v>
       </c>
       <c r="B48" t="n">
         <v>140</v>
       </c>
-      <c r="C48" s="2" t="n"/>
-      <c r="D48" s="2" t="n">
-        <v>37102000</v>
-      </c>
+      <c r="C48" s="2" t="n">
+        <v>59072000</v>
+      </c>
+      <c r="D48" s="2" t="n"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Jizzax Yog'och MChJ</t>
+          <t>Mehnat Non MChJ</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>362365657</t>
+          <t>267657283</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>20208000386072293001</t>
+          <t>20208000254733554001</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №182/26, НДС 12%</t>
+          <t>Оплата за упаковочные материалы, с/ф №6487</t>
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>107397000</v>
+        <v>96672000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
-        <v>46230</v>
+        <v>46226</v>
       </c>
       <c r="B49" t="n">
         <v>141</v>
       </c>
       <c r="C49" s="2" t="n"/>
       <c r="D49" s="2" t="n">
-        <v>5681000</v>
+        <v>5837000</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Nurafshon Metall MChJ</t>
+          <t>Chust Mebel MChJ</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>325368505</t>
+          <t>395380844</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20208000246078378001</t>
+          <t>20208000235273440001</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №7214 27.07.2026, QQS bilan</t>
+          <t>Предоплата за товар по договору №89/26 от 23.07.2026</t>
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>113078000</v>
+        <v>102509000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
-        <v>46230</v>
+        <v>46226</v>
       </c>
       <c r="B50" t="n">
         <v>142</v>
       </c>
-      <c r="C50" s="2" t="n">
-        <v>2227000</v>
-      </c>
-      <c r="D50" s="2" t="n"/>
+      <c r="C50" s="2" t="n"/>
+      <c r="D50" s="2" t="n">
+        <v>4136000</v>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Saodat Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>256884648</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20208000572345125001</t>
+          <t>20208000716469607001</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchun to'lov iyul</t>
+          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №466 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>110851000</v>
+        <v>106645000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
-        <v>46232</v>
+        <v>46226</v>
       </c>
       <c r="B51" t="n">
         <v>143</v>
       </c>
-      <c r="C51" s="2" t="n"/>
-      <c r="D51" s="2" t="n">
-        <v>17911000</v>
-      </c>
+      <c r="C51" s="2" t="n">
+        <v>5846000</v>
+      </c>
+      <c r="D51" s="2" t="n"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Nurafshon Metall MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>325368505</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>20208000246078378001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №56/26, QQS 12%</t>
+          <t>НДС ЗА ИЮНЬ 2026 Г.</t>
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>128762000</v>
+        <v>100799000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="n">
-        <v>46233</v>
+        <v>46230</v>
       </c>
       <c r="B52" t="n">
         <v>144</v>
       </c>
-      <c r="C52" s="2" t="n">
-        <v>22636000</v>
-      </c>
-      <c r="D52" s="2" t="n"/>
+      <c r="C52" s="2" t="n"/>
+      <c r="D52" s="2" t="n">
+        <v>33112000</v>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Oqtosh Agro Servis XK</t>
+          <t>Zarafshon Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>225285737</t>
+          <t>336850572</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>20208000715149282001</t>
+          <t>20208000607837882001</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №244/26, QQS bilan</t>
+          <t>Оплата за продукцию по договору №245/26, ДС 12%</t>
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>106126000</v>
+        <v>133911000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="n">
-        <v>46234</v>
+        <v>46230</v>
       </c>
       <c r="B53" t="n">
         <v>145</v>
       </c>
       <c r="C53" s="2" t="n"/>
       <c r="D53" s="2" t="n">
-        <v>51499000</v>
+        <v>6098000</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Nurafshon Metall MChJ</t>
+          <t>Zarafshon Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>325368505</t>
+          <t>336850572</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>20208000246078378001</t>
+          <t>20208000607837882001</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №215/26, QQS 12%</t>
+          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №79/26, НДС 12%</t>
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>157625000</v>
+        <v>140009000</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
-        <v>46234</v>
+        <v>46230</v>
       </c>
       <c r="B54" t="n">
         <v>146</v>
       </c>
-      <c r="C54" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D54" s="2" t="n"/>
+      <c r="C54" s="2" t="n"/>
+      <c r="D54" s="2" t="n">
+        <v>3236000</v>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Sarbon Moliya Bank</t>
+          <t>Zarafshon Avto Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>336850572</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000607837882001</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Комиссия банка за расчетно-кассовое обслуживание за июль</t>
+          <t>Оплата по с/ф №7715 за поставленный товар</t>
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>157325000</v>
+        <v>143245000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
-        <v>46237</v>
+        <v>46230</v>
       </c>
       <c r="B55" t="n">
         <v>147</v>
       </c>
-      <c r="C55" s="2" t="n"/>
-      <c r="D55" s="2" t="n">
-        <v>115329000</v>
-      </c>
+      <c r="C55" s="2" t="n">
+        <v>2227000</v>
+      </c>
+      <c r="D55" s="2" t="n"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Bahor Yog' Zavodi MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>330568846</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>20208000807164696001</t>
+          <t>20208000092438345001</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №2036</t>
+          <t>Оплата за электроэнергию за июль 2026 г.</t>
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>272654000</v>
+        <v>141018000</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="n">
-        <v>46237</v>
+        <v>46230</v>
       </c>
       <c r="B56" t="n">
         <v>148</v>
       </c>
-      <c r="C56" s="2" t="n"/>
-      <c r="D56" s="2" t="n">
-        <v>10261000</v>
-      </c>
+      <c r="C56" s="2" t="n">
+        <v>5467000</v>
+      </c>
+      <c r="D56" s="2" t="n"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Oqtosh Oziq-ovqat Savdo MChJ</t>
+          <t>Mehnat Non MChJ</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>372373783</t>
+          <t>267657283</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>20208000390735515001</t>
+          <t>20208000254733554001</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №5976 от 03.08.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за сырье по договору №77/26 от 27.07.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>282915000</v>
+        <v>135551000</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
-        <v>46237</v>
+        <v>46230</v>
       </c>
       <c r="B57" t="n">
         <v>149</v>
       </c>
       <c r="C57" s="2" t="n">
-        <v>12537000</v>
+        <v>11280000</v>
       </c>
       <c r="D57" s="2" t="n"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Mehnat Polimer MChJ</t>
+          <t>Lazzat Oziq-ovqat Savdo AJ</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>267270449</t>
+          <t>331053414</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>20208000582882038001</t>
+          <t>20208000402896757001</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №12/26, QQS bilan</t>
+          <t>ОПЛАТА ЗА УПАКОВОЧНЫЕ МАТЕРИАЛЫ, С/Ф №6090</t>
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>270378000</v>
+        <v>124271000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="n">
-        <v>46237</v>
+        <v>46230</v>
       </c>
       <c r="B58" t="n">
         <v>150</v>
       </c>
       <c r="C58" s="2" t="n">
-        <v>15256000</v>
+        <v>13702000</v>
       </c>
       <c r="D58" s="2" t="n"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Oqtosh Agro Servis XK</t>
+          <t>Tong Savdo AJ</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>225285737</t>
+          <t>281252850</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>20208000715149282001</t>
+          <t>20208000537007953001</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №35/26, QQS bilan</t>
+          <t>Оплата за сырье по договору №26/26 от 27.07.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>255122000</v>
+        <v>110569000</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
-        <v>46237</v>
+        <v>46231</v>
       </c>
       <c r="B59" t="n">
         <v>151</v>
       </c>
-      <c r="C59" s="2" t="n">
-        <v>33936000</v>
-      </c>
-      <c r="D59" s="2" t="n"/>
+      <c r="C59" s="2" t="n"/>
+      <c r="D59" s="2" t="n">
+        <v>33139000</v>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Mehnat Polimer MChJ</t>
+          <t>Zarafshon Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>267270449</t>
+          <t>336850572</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>20208000582882038001</t>
+          <t>20208000607837882001</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №3401</t>
+          <t>Оплата за товар по счет-фактуре №8437 от 28.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>221186000</v>
+        <v>143708000</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="n">
-        <v>46237</v>
+        <v>46232</v>
       </c>
       <c r="B60" t="n">
         <v>152</v>
       </c>
-      <c r="C60" s="2" t="n">
-        <v>38278000</v>
-      </c>
-      <c r="D60" s="2" t="n"/>
+      <c r="C60" s="2" t="n"/>
+      <c r="D60" s="2" t="n">
+        <v>31030000</v>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Mehnat Polimer MChJ</t>
+          <t>Zarafshon Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>267270449</t>
+          <t>336850572</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>20208000582882038001</t>
+          <t>20208000607837882001</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №7473</t>
+          <t>Оплата за продукцию по договору №164/26, НДС 12%</t>
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>182908000</v>
+        <v>174738000</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="n">
-        <v>46238</v>
+        <v>46232</v>
       </c>
       <c r="B61" t="n">
         <v>153</v>
       </c>
       <c r="C61" s="2" t="n"/>
       <c r="D61" s="2" t="n">
-        <v>7336000</v>
+        <v>3817000</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Nurafshon Metall MChJ</t>
+          <t>Chust Mebel MChJ</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>325368505</t>
+          <t>395380844</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>20208000246078378001</t>
+          <t>20208000235273440001</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №5523 04.08.2026, QQS bilan</t>
+          <t>Оплата за продукцию по дог. №223/26, НДС 12%</t>
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>190244000</v>
+        <v>178555000</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="n">
-        <v>46238</v>
+        <v>46233</v>
       </c>
       <c r="B62" t="n">
         <v>154</v>
       </c>
-      <c r="C62" s="2" t="n">
-        <v>14886000</v>
-      </c>
-      <c r="D62" s="2" t="n"/>
+      <c r="C62" s="2" t="n"/>
+      <c r="D62" s="2" t="n">
+        <v>12761000</v>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Mehnat Polimer MChJ</t>
+          <t>Zarafshon Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>267270449</t>
+          <t>336850572</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>20208000582882038001</t>
+          <t>20208000607837882001</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №207/26</t>
+          <t>Shartnoma №182/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>175358000</v>
+        <v>191316000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
-        <v>46240</v>
+        <v>46233</v>
       </c>
       <c r="B63" t="n">
         <v>155</v>
       </c>
       <c r="C63" s="2" t="n">
-        <v>18878000</v>
+        <v>34027000</v>
       </c>
       <c r="D63" s="2" t="n"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Sarbon Moliya Bank</t>
+          <t>Tong Savdo AJ</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>281252850</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000537007953001</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Ish haqi to'lovi iyul 2026 (plastik kartalarga)</t>
+          <t>Оплата за товары согласно с/ф №5790</t>
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>156480000</v>
+        <v>157289000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="n">
-        <v>46241</v>
+        <v>46234</v>
       </c>
       <c r="B64" t="n">
         <v>156</v>
       </c>
       <c r="C64" s="2" t="n"/>
       <c r="D64" s="2" t="n">
-        <v>29732000</v>
+        <v>23888000</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Nihol Oziq-ovqat Savdo AJ</t>
+          <t>Chust Mebel MChJ</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>349483499</t>
+          <t>395380844</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>20208000682636274001</t>
+          <t>20208000235273440001</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>SHARTNOMA №25/26 BO'YICHA OLDINDAN TO'LOV</t>
+          <t>Оплата за товар по счет-фактуре №8043 от 31.072026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>186212000</v>
+        <v>181177000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="n">
-        <v>46241</v>
+        <v>46234</v>
       </c>
       <c r="B65" t="n">
         <v>157</v>
       </c>
-      <c r="C65" s="2" t="n"/>
-      <c r="D65" s="2" t="n">
-        <v>7891000</v>
-      </c>
+      <c r="C65" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D65" s="2" t="n"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Nurafshon Metall MChJ</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>325368505</t>
+          <t>Sarbon Moliya Bank</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>20208000246078378001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №268/26, QQS 12%</t>
+          <t>Плат за SMS-информирование</t>
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>194103000</v>
+        <v>180877000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="n">
-        <v>46241</v>
+        <v>46234</v>
       </c>
       <c r="B66" t="n">
         <v>158</v>
       </c>
       <c r="C66" s="2" t="n">
-        <v>3294000</v>
+        <v>15169000</v>
       </c>
       <c r="D66" s="2" t="n"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Olmaliq Qurilish MChJ</t>
+          <t>Mehnat Non MChJ</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>359731053</t>
+          <t>267657283</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>20208000149402896001</t>
+          <t>20208000254733554001</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Bino ijarasi uchun to'lov avgust</t>
+          <t>Оплата за товары согласно счет-фактуре №1731</t>
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>190809000</v>
+        <v>165708000</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="n">
-        <v>46241</v>
+        <v>46237</v>
       </c>
       <c r="B67" t="n">
         <v>159</v>
       </c>
-      <c r="C67" s="2" t="n">
-        <v>4640000</v>
-      </c>
-      <c r="D67" s="2" t="n"/>
+      <c r="C67" s="2" t="n"/>
+      <c r="D67" s="2" t="n">
+        <v>38929000</v>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Mehnat Polimer MChJ</t>
+          <t>Zarafshon Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>267270449</t>
+          <t>336850572</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>20208000582882038001</t>
+          <t>20208000607837882001</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №51/26</t>
+          <t>Оплата за товар по счет-фактуре №6500 от 03.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>186169000</v>
+        <v>204637000</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="n">
-        <v>46244</v>
+        <v>46237</v>
       </c>
       <c r="B68" t="n">
         <v>160</v>
       </c>
       <c r="C68" s="2" t="n"/>
       <c r="D68" s="2" t="n">
-        <v>26462000</v>
+        <v>10802000</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Nurafshon Metall MChJ</t>
+          <t>Zarafshon Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>325368505</t>
+          <t>336850572</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>20208000246078378001</t>
+          <t>20208000607837882001</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №249/26, НДС 12%</t>
+          <t>Оплата за продукцию по договору №186/26, НДС 12%</t>
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>212631000</v>
+        <v>215439000</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="n">
-        <v>46244</v>
+        <v>46237</v>
       </c>
       <c r="B69" t="n">
         <v>161</v>
       </c>
-      <c r="C69" s="2" t="n">
-        <v>9142000</v>
-      </c>
-      <c r="D69" s="2" t="n"/>
+      <c r="C69" s="2" t="n"/>
+      <c r="D69" s="2" t="n">
+        <v>6841000</v>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Mehnat Polimer MChJ</t>
+          <t>Zarafshon Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>267270449</t>
+          <t>336850572</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>20208000582882038001</t>
+          <t>20208000607837882001</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №84/26</t>
+          <t>Оплата за продукцию по дог. №231/26, НДС 12%</t>
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>203489000</v>
+        <v>222280000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="n">
-        <v>46245</v>
+        <v>46237</v>
       </c>
       <c r="B70" t="n">
         <v>162</v>
       </c>
-      <c r="C70" s="2" t="n">
-        <v>11862000</v>
-      </c>
-      <c r="D70" s="2" t="n"/>
+      <c r="C70" s="2" t="n"/>
+      <c r="D70" s="2" t="n">
+        <v>2923000</v>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Oqtosh Agro Servis XK</t>
+          <t>Zarafshon Agro Servis MChJ</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>225285737</t>
+          <t>327044975</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>20208000715149282001</t>
+          <t>20208000288203850001</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>TOVARLAR UCHUN TO'LOV H/F №4154</t>
+          <t>Оплата за товар по счет-фактуре №8044 от 03.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>191627000</v>
+        <v>225203000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="n">
-        <v>46245</v>
+        <v>46237</v>
       </c>
       <c r="B71" t="n">
         <v>163</v>
       </c>
       <c r="C71" s="2" t="n">
-        <v>35861000</v>
+        <v>323141000</v>
       </c>
       <c r="D71" s="2" t="n"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Mehnat Polimer MChJ</t>
+          <t>Tong Savdo AJ</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>267270449</t>
+          <t>281252850</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>20208000582882038001</t>
+          <t>20208000537007953001</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Оплата за сырье по дог. №285/26 от 11.08.2026, НДС 12%</t>
+          <t>Оплата за сырье по договору №154/26 от 03.08.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>155766000</v>
+        <v>-97938000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="n">
-        <v>46246</v>
+        <v>46238</v>
       </c>
       <c r="B72" t="n">
         <v>164</v>
       </c>
       <c r="C72" s="2" t="n"/>
       <c r="D72" s="2" t="n">
-        <v>17656000</v>
+        <v>12135000</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Bahor Yog' Zavodi MChJ</t>
+          <t>Zarafshon Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>330568846</t>
+          <t>336850572</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>20208000807164696001</t>
+          <t>20208000607837882001</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3106,632 +3111,632 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №128/26, QQS 12%</t>
+          <t>Оплата по счет-фактуре №2467 за поставленный товар</t>
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>173422000</v>
+        <v>-85803000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="n">
-        <v>46247</v>
+        <v>46238</v>
       </c>
       <c r="B73" t="n">
         <v>165</v>
       </c>
       <c r="C73" s="2" t="n">
-        <v>8343000</v>
+        <v>13069000</v>
       </c>
       <c r="D73" s="2" t="n"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Mehnat Polimer MChJ</t>
+          <t>Lazzat Oziq-ovqat Savdo AJ</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>267270449</t>
+          <t>331053414</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>20208000582882038001</t>
+          <t>20208000402896757001</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №269/26 от 13.08.2026, НДС 12%</t>
+          <t>Оплата за сырье по дог. №289/26 от 04.08.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>165079000</v>
+        <v>-98872000</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="n">
-        <v>46248</v>
+        <v>46239</v>
       </c>
       <c r="B74" t="n">
         <v>166</v>
       </c>
       <c r="C74" s="2" t="n">
-        <v>11323000</v>
+        <v>18878000</v>
       </c>
       <c r="D74" s="2" t="n"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Mehnat Polimer MChJ</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>267270449</t>
+          <t>Sarbon Moliya Bank</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>20208000582882038001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по дог. №151/26</t>
+          <t>Перечисление заработной платы за июль 2026 г. согласно реестру №5292</t>
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>153756000</v>
+        <v>-117750000</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="n">
-        <v>46251</v>
+        <v>46241</v>
       </c>
       <c r="B75" t="n">
         <v>167</v>
       </c>
       <c r="C75" s="2" t="n"/>
       <c r="D75" s="2" t="n">
-        <v>24082000</v>
+        <v>4387000</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Jizzax Yog'och MChJ</t>
+          <t>Zarafshon Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>362365657</t>
+          <t>336850572</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>20208000386072293001</t>
+          <t>20208000607837882001</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №2320 17.08.2026, QQS bilan</t>
+          <t>Предоплата за товар по договору №51/26 от 07.08.2026</t>
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>177838000</v>
+        <v>-113363000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="n">
-        <v>46251</v>
+        <v>46244</v>
       </c>
       <c r="B76" t="n">
         <v>168</v>
       </c>
       <c r="C76" s="2" t="n"/>
       <c r="D76" s="2" t="n">
-        <v>14034000</v>
+        <v>9217000</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Nurafshon Metall MChJ</t>
+          <t>Saodat Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>325368505</t>
+          <t>256884648</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>20208000246078378001</t>
+          <t>20208000716469607001</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №260/26, НДС 12%</t>
+          <t>Shartnoma №104/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>191872000</v>
+        <v>-104146000</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="n">
-        <v>46251</v>
+        <v>46244</v>
       </c>
       <c r="B77" t="n">
         <v>169</v>
       </c>
-      <c r="C77" s="2" t="n">
-        <v>2574000</v>
-      </c>
-      <c r="D77" s="2" t="n"/>
+      <c r="C77" s="2" t="n"/>
+      <c r="D77" s="2" t="n">
+        <v>7010000</v>
+      </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Zarafshon Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>336850572</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000607837882001</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Iyul oyi uchun ijtimoiy soliq</t>
+          <t>Предоплата за товар по договору №84/26 от 10.08.2026</t>
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>189298000</v>
+        <v>-97136000</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="n">
-        <v>46251</v>
+        <v>46244</v>
       </c>
       <c r="B78" t="n">
         <v>170</v>
       </c>
-      <c r="C78" s="2" t="n">
-        <v>2574000</v>
-      </c>
-      <c r="D78" s="2" t="n"/>
+      <c r="C78" s="2" t="n"/>
+      <c r="D78" s="2" t="n">
+        <v>5523000</v>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Zarafshon Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>336850572</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000607837882001</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Jismoniy shaxslar daromad solig'i iyul 2026</t>
+          <t>Оплата за товар по счет-фактуре №8573 от 10.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>186724000</v>
+        <v>-91613000</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="n">
-        <v>46252</v>
+        <v>46244</v>
       </c>
       <c r="B79" t="n">
         <v>171</v>
       </c>
       <c r="C79" s="2" t="n"/>
       <c r="D79" s="2" t="n">
-        <v>81603000</v>
+        <v>3625000</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Jizzax Yog'och MChJ</t>
+          <t>Zarafshon Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>362365657</t>
+          <t>336850572</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>20208000386072293001</t>
+          <t>20208000607837882001</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Mahsulot uchu to'lov, shartnoma №233/26, QQS 12%</t>
+          <t>Mahsulot uchun to'lov, shartn. №139/26, QQS 12%</t>
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>268327000</v>
+        <v>-87988000</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="n">
-        <v>46252</v>
+        <v>46244</v>
       </c>
       <c r="B80" t="n">
         <v>172</v>
       </c>
-      <c r="C80" s="2" t="n"/>
-      <c r="D80" s="2" t="n">
-        <v>12959000</v>
-      </c>
+      <c r="C80" s="2" t="n">
+        <v>3294000</v>
+      </c>
+      <c r="D80" s="2" t="n"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Nurafshon Metall MChJ</t>
+          <t>Durdona Qurilish MChJ</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>325368505</t>
+          <t>312569656</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>20208000246078378001</t>
+          <t>20208000417219297001</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №217/26, QQS 12%</t>
+          <t>Bino ijarasi uchun to'lov avgust</t>
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>281286000</v>
+        <v>-91282000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="n">
-        <v>46252</v>
+        <v>46245</v>
       </c>
       <c r="B81" t="n">
         <v>173</v>
       </c>
-      <c r="C81" s="2" t="n">
-        <v>20491000</v>
-      </c>
-      <c r="D81" s="2" t="n"/>
+      <c r="C81" s="2" t="n"/>
+      <c r="D81" s="2" t="n">
+        <v>59524000</v>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Mehnat Polimer MChJ</t>
+          <t>Zarafshon Agro Servis MChJ</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>267270449</t>
+          <t>327044975</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>20208000582882038001</t>
+          <t>20208000288203850001</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №8680</t>
+          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №4/26, НДС 12%</t>
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>260795000</v>
+        <v>-31758000</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="n">
-        <v>46253</v>
+        <v>46245</v>
       </c>
       <c r="B82" t="n">
         <v>174</v>
       </c>
       <c r="C82" s="2" t="n"/>
       <c r="D82" s="2" t="n">
-        <v>20995000</v>
+        <v>30625000</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Nihol Sut Mahsulotlari MChJ</t>
+          <t>Zarafshon Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>308432682</t>
+          <t>336850572</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>20208000052496380001</t>
+          <t>20208000607837882001</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>SHARTNOMA №5/26 BO'YICHA OLDINDAN TO'LOV</t>
+          <t>Tovar uchun to'lov, h/f №7941 11.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>281790000</v>
+        <v>-1133000</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="n">
-        <v>46253</v>
+        <v>46245</v>
       </c>
       <c r="B83" t="n">
         <v>175</v>
       </c>
-      <c r="C83" s="2" t="n">
-        <v>9248000</v>
-      </c>
-      <c r="D83" s="2" t="n"/>
+      <c r="C83" s="2" t="n"/>
+      <c r="D83" s="2" t="n">
+        <v>20234000</v>
+      </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Mehnat Polimer MChJ</t>
+          <t>Zarafshon Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>267270449</t>
+          <t>336850572</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>20208000582882038001</t>
+          <t>20208000607837882001</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №44/26, QQS bilan</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №8092</t>
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>272542000</v>
+        <v>19101000</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="n">
-        <v>46254</v>
+        <v>46246</v>
       </c>
       <c r="B84" t="n">
         <v>176</v>
       </c>
-      <c r="C84" s="2" t="n">
-        <v>33500000</v>
-      </c>
-      <c r="D84" s="2" t="n"/>
+      <c r="C84" s="2" t="n"/>
+      <c r="D84" s="2" t="n">
+        <v>12111000</v>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-5531)</t>
+          <t>Zarafshon Avto Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>336850572</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>16307000202482792417</t>
+          <t>20208000607837882001</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-5531 bo'yicha navbatdagi to'lov (08.2026)</t>
+          <t>Предоплата за товар по договору №68/26 от 12.08.2026</t>
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>239042000</v>
+        <v>31212000</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="n">
-        <v>46255</v>
+        <v>46246</v>
       </c>
       <c r="B85" t="n">
         <v>177</v>
       </c>
       <c r="C85" s="2" t="n"/>
       <c r="D85" s="2" t="n">
-        <v>24262000</v>
+        <v>9307000</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Nurafshon Metall MChJ</t>
+          <t>Zarafshon Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>325368505</t>
+          <t>336850572</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>20208000246078378001</t>
+          <t>20208000607837882001</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №68/26, QQS 12%</t>
+          <t>Yetkazigan tovar uchun to'lov h/f №3498</t>
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>263304000</v>
+        <v>40519000</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="n">
-        <v>46255</v>
+        <v>46246</v>
       </c>
       <c r="B86" t="n">
         <v>178</v>
       </c>
-      <c r="C86" s="2" t="n">
-        <v>5999000</v>
-      </c>
-      <c r="D86" s="2" t="n"/>
+      <c r="C86" s="2" t="n"/>
+      <c r="D86" s="2" t="n">
+        <v>7574000</v>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Oqtosh Agro Servis XK</t>
+          <t>Kattaqo'rg'on Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>225285737</t>
+          <t>348349936</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>20208000715149282001</t>
+          <t>20208000263627433001</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №216/26 от 21.08.2026, НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №5780 от 12.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>257305000</v>
+        <v>48093000</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="n">
-        <v>46258</v>
+        <v>46247</v>
       </c>
       <c r="B87" t="n">
         <v>179</v>
       </c>
-      <c r="C87" s="2" t="n"/>
-      <c r="D87" s="2" t="n">
-        <v>48989000</v>
-      </c>
+      <c r="C87" s="2" t="n">
+        <v>19907000</v>
+      </c>
+      <c r="D87" s="2" t="n"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Nurafshon Metall MChJ</t>
+          <t>Tong Savdo AJ</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>325368505</t>
+          <t>281252850</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>20208000246078378001</t>
+          <t>20208000537007953001</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №194/26, QQS 12%</t>
+          <t>Оплата за товары согласно счет-фактуре №3650</t>
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>306294000</v>
+        <v>28186000</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="n">
-        <v>46258</v>
+        <v>46248</v>
       </c>
       <c r="B88" t="n">
         <v>180</v>
       </c>
       <c r="C88" s="2" t="n"/>
       <c r="D88" s="2" t="n">
-        <v>10344000</v>
+        <v>25193000</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Bahor Yog' Zavodi MChJ</t>
+          <t>Zarafshon Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>330568846</t>
+          <t>336850572</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>20208000807164696001</t>
+          <t>20208000607837882001</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -3741,62 +3746,62 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №128 от 24.08.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за продукцию по договору №157/26, НДС 12%</t>
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>316638000</v>
+        <v>53379000</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="n">
-        <v>46258</v>
+        <v>46248</v>
       </c>
       <c r="B89" t="n">
         <v>181</v>
       </c>
       <c r="C89" s="2" t="n">
-        <v>2059000</v>
+        <v>2574000</v>
       </c>
       <c r="D89" s="2" t="n"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>20208000572345125001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchun to'lov avgust</t>
+          <t>Ijtimoiy soliq iyul 2026</t>
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>314579000</v>
+        <v>50805000</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="n">
-        <v>46258</v>
+        <v>46248</v>
       </c>
       <c r="B90" t="n">
         <v>182</v>
       </c>
       <c r="C90" s="2" t="n">
-        <v>5423000</v>
+        <v>2574000</v>
       </c>
       <c r="D90" s="2" t="n"/>
       <c r="E90" t="inlineStr">
@@ -3821,197 +3826,192 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>НДС за июль 2026 г.</t>
+          <t>НДФЛ за июль 2026</t>
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>309156000</v>
+        <v>48231000</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="n">
-        <v>46258</v>
+        <v>46248</v>
       </c>
       <c r="B91" t="n">
         <v>183</v>
       </c>
       <c r="C91" s="2" t="n">
-        <v>28810000</v>
+        <v>14052000</v>
       </c>
       <c r="D91" s="2" t="n"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Mehnat Polimer MChJ</t>
+          <t>Mehnat Non MChJ</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>267270449</t>
+          <t>267657283</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>20208000582882038001</t>
+          <t>20208000254733554001</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №194/26, QQS bilan</t>
+          <t>ПРЕДОПЛАТА ЗА МАТЕРИАЛЫ ПО ДОГ. №278/26</t>
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>280346000</v>
+        <v>34179000</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="n">
-        <v>46261</v>
+        <v>46251</v>
       </c>
       <c r="B92" t="n">
         <v>184</v>
       </c>
       <c r="C92" s="2" t="n">
-        <v>7088000</v>
+        <v>5450000</v>
       </c>
       <c r="D92" s="2" t="n"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Mehnat Polimer MChJ</t>
+          <t>Lazzat Oziq-ovqat Savdo AJ</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>267270449</t>
+          <t>331053414</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>20208000582882038001</t>
+          <t>20208000402896757001</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №186/26 от 27.08.2026, НДС 12%</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №283/26, QQS bilan</t>
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>273258000</v>
+        <v>28729000</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="n">
-        <v>46261</v>
+        <v>46252</v>
       </c>
       <c r="B93" t="n">
         <v>185</v>
       </c>
-      <c r="C93" s="2" t="n">
-        <v>20045000</v>
-      </c>
-      <c r="D93" s="2" t="n"/>
+      <c r="C93" s="2" t="n"/>
+      <c r="D93" s="2" t="n">
+        <v>21667000</v>
+      </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Mehnat Polimer MChJ</t>
+          <t>Zarafshon Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>267270449</t>
+          <t>336850572</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>20208000582882038001</t>
+          <t>20208000607837882001</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №247/26</t>
+          <t>Оплата за продукцию по дог. №5/26, НДС 12%</t>
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>253213000</v>
+        <v>50396000</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="n">
-        <v>46262</v>
+        <v>46253</v>
       </c>
       <c r="B94" t="n">
         <v>186</v>
       </c>
-      <c r="C94" s="2" t="n">
-        <v>26637000</v>
-      </c>
-      <c r="D94" s="2" t="n"/>
+      <c r="C94" s="2" t="n"/>
+      <c r="D94" s="2" t="n">
+        <v>17407000</v>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Shodlik Agro Servis MChJ</t>
+          <t>Zarafshon Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>284812528</t>
+          <t>336850572</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>20208000015370079001</t>
+          <t>20208000607837882001</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №109/26, QQS bilan</t>
+          <t>Оплата за товар по счет-фактуре №8748 от 19.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J94" s="2" t="n">
-        <v>226576000</v>
+        <v>67803000</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="n">
-        <v>46262</v>
+        <v>46254</v>
       </c>
       <c r="B95" t="n">
         <v>187</v>
       </c>
       <c r="C95" s="2" t="n">
-        <v>41709000</v>
+        <v>33500000</v>
       </c>
       <c r="D95" s="2" t="n"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Farovon Metall Servis MChJ</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>252676572</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-5531)</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>20208000362547335001</t>
+          <t>16307000202482792417</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4021,32 +4021,37 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №25/26, QQS bilan</t>
+          <t>Kredit shartnomasi L-2025-5531 bo'yicha navbatdagi to'lov (08.2026)</t>
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>184867000</v>
+        <v>34303000</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="n">
-        <v>46265</v>
+        <v>46255</v>
       </c>
       <c r="B96" t="n">
         <v>188</v>
       </c>
-      <c r="C96" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D96" s="2" t="n"/>
+      <c r="C96" s="2" t="n"/>
+      <c r="D96" s="2" t="n">
+        <v>8994000</v>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Sarbon Moliya Bank</t>
+          <t>Andijon Avto Savdo XK</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>237378303</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000073551515001</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -4056,517 +4061,517 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Hisob-kassa xizmati uchun haq</t>
+          <t>Tovar uchun to'lov, hisob-faktura №4615 21.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>184567000</v>
+        <v>43297000</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="n">
-        <v>46265</v>
+        <v>46255</v>
       </c>
       <c r="B97" t="n">
         <v>189</v>
       </c>
       <c r="C97" s="2" t="n">
-        <v>12878000</v>
+        <v>5454000</v>
       </c>
       <c r="D97" s="2" t="n"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Shodlik Agro Servis MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>284812528</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>20208000015370079001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №220/26 от 31.08.2026, НДС 12%</t>
+          <t>Уплата налога на добавленную стоимость за июль</t>
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>171689000</v>
+        <v>37843000</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="n">
-        <v>46265</v>
+        <v>46258</v>
       </c>
       <c r="B98" t="n">
         <v>190</v>
       </c>
-      <c r="C98" s="2" t="n">
-        <v>33491000</v>
-      </c>
-      <c r="D98" s="2" t="n"/>
+      <c r="C98" s="2" t="n"/>
+      <c r="D98" s="2" t="n">
+        <v>20285000</v>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Mehnat Polimer MChJ</t>
+          <t>Zarafshon Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>267270449</t>
+          <t>336850572</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>20208000582882038001</t>
+          <t>20208000607837882001</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartn. №199/26, QQS bilan</t>
+          <t>Оплата за товар по счет-фактуре №9467 от 24.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>138198000</v>
+        <v>58128000</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="n">
-        <v>46266</v>
+        <v>46258</v>
       </c>
       <c r="B99" t="n">
         <v>191</v>
       </c>
       <c r="C99" s="2" t="n"/>
       <c r="D99" s="2" t="n">
-        <v>13285000</v>
+        <v>12380000</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Chirchiq Mato XK</t>
+          <t>Zarafshon Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>245637587</t>
+          <t>336850572</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>20208000286988280001</t>
+          <t>20208000607837882001</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №146/26, QQS 12%</t>
+          <t>Оплата за товар по счет-фактуре №2653 от 24.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>151483000</v>
+        <v>70508000</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="n">
-        <v>46266</v>
+        <v>46258</v>
       </c>
       <c r="B100" t="n">
         <v>192</v>
       </c>
-      <c r="C100" s="2" t="n">
-        <v>6515000</v>
-      </c>
-      <c r="D100" s="2" t="n"/>
+      <c r="C100" s="2" t="n"/>
+      <c r="D100" s="2" t="n">
+        <v>5587000</v>
+      </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Mehnat Polimer MChJ</t>
+          <t>Zarafshon Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>267270449</t>
+          <t>336850572</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>20208000582882038001</t>
+          <t>20208000607837882001</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №1666</t>
+          <t>Оплата за продукцию по договору №29/26, НДС 12%</t>
         </is>
       </c>
       <c r="J100" s="2" t="n">
-        <v>144968000</v>
+        <v>76095000</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="n">
-        <v>46267</v>
+        <v>46258</v>
       </c>
       <c r="B101" t="n">
         <v>193</v>
       </c>
       <c r="C101" s="2" t="n"/>
       <c r="D101" s="2" t="n">
-        <v>9307000</v>
+        <v>2803000</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Jizzax Yog'och MChJ</t>
+          <t>Zarafshon Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>362365657</t>
+          <t>336850572</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>20208000386072293001</t>
+          <t>20208000607837882001</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №1067 02.09.2026, QQS bilan</t>
+          <t>Оплата по счет-фактуре №5429 за поставленный товар</t>
         </is>
       </c>
       <c r="J101" s="2" t="n">
-        <v>154275000</v>
+        <v>78898000</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="n">
-        <v>46268</v>
+        <v>46258</v>
       </c>
       <c r="B102" t="n">
         <v>194</v>
       </c>
-      <c r="C102" s="2" t="n"/>
-      <c r="D102" s="2" t="n">
-        <v>50188000</v>
-      </c>
+      <c r="C102" s="2" t="n">
+        <v>2059000</v>
+      </c>
+      <c r="D102" s="2" t="n"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Nurafshon Metall MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>325368505</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>20208000246078378001</t>
+          <t>20208000092438345001</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №4152</t>
+          <t>Оплата за электроэнергию согласно счету</t>
         </is>
       </c>
       <c r="J102" s="2" t="n">
-        <v>204463000</v>
+        <v>76839000</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="n">
-        <v>46268</v>
+        <v>46260</v>
       </c>
       <c r="B103" t="n">
         <v>195</v>
       </c>
       <c r="C103" s="2" t="n"/>
       <c r="D103" s="2" t="n">
-        <v>27720000</v>
+        <v>23127000</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Nihol Oziq-ovqat Savdo AJ</t>
+          <t>Saodat Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>349483499</t>
+          <t>256884648</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>20208000682636274001</t>
+          <t>20208000716469607001</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №5816 за поставленный товар</t>
+          <t>Tovar uchun to'lov, hisob-faktura №5760 26.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J103" s="2" t="n">
-        <v>232183000</v>
+        <v>99966000</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="n">
-        <v>46268</v>
+        <v>46260</v>
       </c>
       <c r="B104" t="n">
         <v>196</v>
       </c>
       <c r="C104" s="2" t="n">
-        <v>9938000</v>
+        <v>15060000</v>
       </c>
       <c r="D104" s="2" t="n"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Mehnat Polimer MChJ</t>
+          <t>Mehnat Non MChJ</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>267270449</t>
+          <t>267657283</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>20208000582882038001</t>
+          <t>20208000254733554001</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №8312</t>
+          <t>Оплата за упаковочные материалы, с/ф №2168</t>
         </is>
       </c>
       <c r="J104" s="2" t="n">
-        <v>222245000</v>
+        <v>84906000</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="n">
-        <v>46268</v>
+        <v>46261</v>
       </c>
       <c r="B105" t="n">
         <v>197</v>
       </c>
-      <c r="C105" s="2" t="n">
-        <v>34135000</v>
-      </c>
-      <c r="D105" s="2" t="n"/>
+      <c r="C105" s="2" t="n"/>
+      <c r="D105" s="2" t="n">
+        <v>16093000</v>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Oqtosh Agro Servis XK</t>
+          <t>Zarafshon Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>225285737</t>
+          <t>336850572</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>20208000715149282001</t>
+          <t>20208000607837882001</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №204/26</t>
+          <t>Tovar uchun to'lov, hisob-faktura №3470 27.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J105" s="2" t="n">
-        <v>188110000</v>
+        <v>100999000</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="n">
-        <v>46269</v>
+        <v>46261</v>
       </c>
       <c r="B106" t="n">
         <v>198</v>
       </c>
-      <c r="C106" s="2" t="n">
-        <v>6922000</v>
-      </c>
-      <c r="D106" s="2" t="n"/>
+      <c r="C106" s="2" t="n"/>
+      <c r="D106" s="2" t="n">
+        <v>5040000</v>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Mehnat Polimer MChJ</t>
+          <t>Zarafshon Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>267270449</t>
+          <t>336850572</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>20208000582882038001</t>
+          <t>20208000607837882001</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №6929</t>
+          <t>Оплата по счет-фактуре №4498 за поставленный товар</t>
         </is>
       </c>
       <c r="J106" s="2" t="n">
-        <v>181188000</v>
+        <v>106039000</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="n">
-        <v>46272</v>
+        <v>46261</v>
       </c>
       <c r="B107" t="n">
         <v>199</v>
       </c>
-      <c r="C107" s="2" t="n"/>
-      <c r="D107" s="2" t="n">
-        <v>81332000</v>
-      </c>
+      <c r="C107" s="2" t="n">
+        <v>3295000</v>
+      </c>
+      <c r="D107" s="2" t="n"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Nurafshon Metall MChJ</t>
+          <t>Tong Savdo AJ</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>325368505</t>
+          <t>281252850</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>20208000246078378001</t>
+          <t>20208000537007953001</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Shartnoma №8/26 bo'yicha oldindan to'lov</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №274/26</t>
         </is>
       </c>
       <c r="J107" s="2" t="n">
-        <v>262520000</v>
+        <v>102744000</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="n">
-        <v>46272</v>
+        <v>46262</v>
       </c>
       <c r="B108" t="n">
         <v>200</v>
       </c>
       <c r="C108" s="2" t="n"/>
       <c r="D108" s="2" t="n">
-        <v>15630000</v>
+        <v>6974000</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Nurafshon Metall MChJ</t>
+          <t>Zarafshon Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>325368505</t>
+          <t>336850572</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>20208000246078378001</t>
+          <t>20208000607837882001</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №6504</t>
+          <t>Tovar uchun to'lov, hisob-faktura №3335 28.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J108" s="2" t="n">
-        <v>278150000</v>
+        <v>109718000</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="n">
-        <v>46272</v>
+        <v>46262</v>
       </c>
       <c r="B109" t="n">
         <v>201</v>
       </c>
-      <c r="C109" s="2" t="n">
-        <v>7885000</v>
-      </c>
-      <c r="D109" s="2" t="n"/>
+      <c r="C109" s="2" t="n"/>
+      <c r="D109" s="2" t="n">
+        <v>3769000</v>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Oqtosh Agro Servis XK</t>
+          <t>Lazzat Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>225285737</t>
+          <t>236565783</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>20208000715149282001</t>
+          <t>20208000607229325001</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -4576,112 +4581,117 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №250/26</t>
+          <t>Оплата за товар по счет-фактуре №9241 от 28.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J109" s="2" t="n">
-        <v>270265000</v>
+        <v>113487000</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="n">
-        <v>46272</v>
+        <v>46262</v>
       </c>
       <c r="B110" t="n">
         <v>202</v>
       </c>
-      <c r="C110" s="2" t="n">
-        <v>10824000</v>
-      </c>
-      <c r="D110" s="2" t="n"/>
+      <c r="C110" s="2" t="n"/>
+      <c r="D110" s="2" t="n">
+        <v>3522000</v>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Meva Eksport MChJ</t>
+          <t>Lazzat Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>282116549</t>
+          <t>236565783</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>20208000195837259001</t>
+          <t>20208000607229325001</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №116/26</t>
+          <t>Оплата за товар по счет-фактуре №254 от 28.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J110" s="2" t="n">
-        <v>259441000</v>
+        <v>117009000</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="n">
-        <v>46272</v>
+        <v>46265</v>
       </c>
       <c r="B111" t="n">
         <v>203</v>
       </c>
-      <c r="C111" s="2" t="n">
-        <v>21309000</v>
-      </c>
-      <c r="D111" s="2" t="n"/>
+      <c r="C111" s="2" t="n"/>
+      <c r="D111" s="2" t="n">
+        <v>20503000</v>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Sarbon Moliya Bank</t>
+          <t>Zarafshon Avto Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>336850572</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000607837882001</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Avgust oyi uchun ish haqi, reestr №7736</t>
+          <t>Оплата за товар по с/ф №8435 от 31.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J111" s="2" t="n">
-        <v>238132000</v>
+        <v>137512000</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="n">
-        <v>46273</v>
+        <v>46265</v>
       </c>
       <c r="B112" t="n">
         <v>204</v>
       </c>
-      <c r="C112" s="2" t="n">
-        <v>3718000</v>
-      </c>
-      <c r="D112" s="2" t="n"/>
+      <c r="C112" s="2" t="n"/>
+      <c r="D112" s="2" t="n">
+        <v>7780000</v>
+      </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Olmaliq Qurilish MChJ</t>
+          <t>Zarafshon Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>359731053</t>
+          <t>336850572</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>20208000149402896001</t>
+          <t>20208000607837882001</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -4691,1152 +4701,1147 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Ijara haqi sentyabr oyi uchun, shartnoma №44/21</t>
+          <t>Оплата за товар по счет-фактуре №3217 от 31.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J112" s="2" t="n">
-        <v>234414000</v>
+        <v>145292000</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="n">
-        <v>46273</v>
+        <v>46265</v>
       </c>
       <c r="B113" t="n">
         <v>205</v>
       </c>
-      <c r="C113" s="2" t="n">
-        <v>122972000</v>
-      </c>
-      <c r="D113" s="2" t="n"/>
+      <c r="C113" s="2" t="n"/>
+      <c r="D113" s="2" t="n">
+        <v>7167000</v>
+      </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Mehnat Polimer MChJ</t>
+          <t>Zarafshon Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>267270449</t>
+          <t>336850572</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>20208000582882038001</t>
+          <t>20208000607837882001</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartn. №59/26, QQS bilan</t>
+          <t>Оплата за товар по счет-фактуре №3732 от 31.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J113" s="2" t="n">
-        <v>111442000</v>
+        <v>152459000</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="3" t="n">
-        <v>46274</v>
+        <v>46265</v>
       </c>
       <c r="B114" t="n">
         <v>206</v>
       </c>
       <c r="C114" s="2" t="n"/>
       <c r="D114" s="2" t="n">
-        <v>17247000</v>
+        <v>5415000</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Chirchiq Mato XK</t>
+          <t>Kattaqo'rg'on Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>245637587</t>
+          <t>348349936</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>20208000286988280001</t>
+          <t>20208000263627433001</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №114/26, QQS 12%</t>
+          <t>Tovar uchun to'lov, hisob-faktura №762 31.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J114" s="2" t="n">
-        <v>128689000</v>
+        <v>157874000</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="3" t="n">
-        <v>46274</v>
+        <v>46265</v>
       </c>
       <c r="B115" t="n">
         <v>207</v>
       </c>
       <c r="C115" s="2" t="n">
-        <v>7580000</v>
+        <v>300000</v>
       </c>
       <c r="D115" s="2" t="n"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Mehnat Polimer MChJ</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>267270449</t>
+          <t>Sarbon Moliya Bank</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>20208000582882038001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №1806</t>
+          <t>Комиссия за перевод</t>
         </is>
       </c>
       <c r="J115" s="2" t="n">
-        <v>121109000</v>
+        <v>157574000</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="3" t="n">
-        <v>46274</v>
+        <v>46265</v>
       </c>
       <c r="B116" t="n">
         <v>208</v>
       </c>
       <c r="C116" s="2" t="n">
-        <v>11821000</v>
+        <v>2211000</v>
       </c>
       <c r="D116" s="2" t="n"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Nukus Poligraf AJ</t>
+          <t>Mehnat Non MChJ</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>217953808</t>
+          <t>267657283</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>20208000462352734001</t>
+          <t>20208000254733554001</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №90/26</t>
+          <t>Оплата за транспортные услуги по дог. №197/26</t>
         </is>
       </c>
       <c r="J116" s="2" t="n">
-        <v>109288000</v>
+        <v>155363000</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="3" t="n">
-        <v>46275</v>
+        <v>46266</v>
       </c>
       <c r="B117" t="n">
         <v>209</v>
       </c>
       <c r="C117" s="2" t="n"/>
       <c r="D117" s="2" t="n">
-        <v>20118000</v>
+        <v>2991000</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Jizzax Yog'och MChJ</t>
+          <t>Zarafshon Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>362365657</t>
+          <t>336850572</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>20208000386072293001</t>
+          <t>20208000607837882001</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №5105 10.09.2026, QQS bilan</t>
+          <t>Предоплата за товар по договору №27/26 от 01.09.2026</t>
         </is>
       </c>
       <c r="J117" s="2" t="n">
-        <v>129406000</v>
+        <v>158354000</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="3" t="n">
-        <v>46276</v>
+        <v>46267</v>
       </c>
       <c r="B118" t="n">
         <v>210</v>
       </c>
-      <c r="C118" s="2" t="n">
-        <v>4411000</v>
-      </c>
-      <c r="D118" s="2" t="n"/>
+      <c r="C118" s="2" t="n"/>
+      <c r="D118" s="2" t="n">
+        <v>16488000</v>
+      </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Mehnat Polimer MChJ</t>
+          <t>Chust Mebel MChJ</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>267270449</t>
+          <t>395380844</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>20208000582882038001</t>
+          <t>20208000235273440001</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №4403</t>
+          <t>Оплата за товар по счет-фактуре №8860 от 02.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J118" s="2" t="n">
-        <v>124995000</v>
+        <v>174842000</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="3" t="n">
-        <v>46276</v>
+        <v>46267</v>
       </c>
       <c r="B119" t="n">
         <v>211</v>
       </c>
       <c r="C119" s="2" t="n">
-        <v>8011000</v>
+        <v>7919000</v>
       </c>
       <c r="D119" s="2" t="n"/>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Mehnat Polimer MChJ</t>
+          <t>Mehnat Non MChJ</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>267270449</t>
+          <t>267657283</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>20208000582882038001</t>
+          <t>20208000254733554001</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №238/26, QQS bilan</t>
+          <t>Предоплата за материалы по дог. №12/26</t>
         </is>
       </c>
       <c r="J119" s="2" t="n">
-        <v>116984000</v>
+        <v>166923000</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="3" t="n">
-        <v>46276</v>
+        <v>46268</v>
       </c>
       <c r="B120" t="n">
         <v>212</v>
       </c>
-      <c r="C120" s="2" t="n">
-        <v>26056000</v>
-      </c>
-      <c r="D120" s="2" t="n"/>
+      <c r="C120" s="2" t="n"/>
+      <c r="D120" s="2" t="n">
+        <v>56625000</v>
+      </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Oqtosh Agro Servis XK</t>
+          <t>Zarafshon Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>225285737</t>
+          <t>336850572</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>20208000715149282001</t>
+          <t>20208000607837882001</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №279/26</t>
+          <t>Оплата по счет-фактуре №2969 за поставленный товар</t>
         </is>
       </c>
       <c r="J120" s="2" t="n">
-        <v>90928000</v>
+        <v>223548000</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="3" t="n">
-        <v>46279</v>
+        <v>46268</v>
       </c>
       <c r="B121" t="n">
         <v>213</v>
       </c>
       <c r="C121" s="2" t="n"/>
       <c r="D121" s="2" t="n">
-        <v>31645000</v>
+        <v>18408000</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Nurafshon Metall MChJ</t>
+          <t>Zarafshon Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>325368505</t>
+          <t>336850572</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>20208000246078378001</t>
+          <t>20208000607837882001</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Shartnoma №208/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата по с/ф №1736 за поставленный товар</t>
         </is>
       </c>
       <c r="J121" s="2" t="n">
-        <v>122573000</v>
+        <v>241956000</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="3" t="n">
-        <v>46279</v>
+        <v>46268</v>
       </c>
       <c r="B122" t="n">
         <v>214</v>
       </c>
       <c r="C122" s="2" t="n">
-        <v>6260000</v>
+        <v>25957000</v>
       </c>
       <c r="D122" s="2" t="n"/>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Mehnat Polimer MChJ</t>
+          <t>Tong Savdo AJ</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>267270449</t>
+          <t>281252850</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>20208000582882038001</t>
+          <t>20208000537007953001</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №96/26, QQS bilan</t>
+          <t>Materiallar uchun oldindan to'lov, shartn. №261/26</t>
         </is>
       </c>
       <c r="J122" s="2" t="n">
-        <v>116313000</v>
+        <v>215999000</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="3" t="n">
-        <v>46279</v>
+        <v>46269</v>
       </c>
       <c r="B123" t="n">
         <v>215</v>
       </c>
-      <c r="C123" s="2" t="n">
-        <v>33111000</v>
-      </c>
-      <c r="D123" s="2" t="n"/>
+      <c r="C123" s="2" t="n"/>
+      <c r="D123" s="2" t="n">
+        <v>13609000</v>
+      </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Meva Eksport MChJ</t>
+          <t>Chust Mebel MChJ</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>282116549</t>
+          <t>395380844</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>20208000195837259001</t>
+          <t>20208000235273440001</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartn. №237/26</t>
+          <t>Предоплата за товар по договору №293/26 от 04.09.2026</t>
         </is>
       </c>
       <c r="J123" s="2" t="n">
-        <v>83202000</v>
+        <v>229608000</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="3" t="n">
-        <v>46280</v>
+        <v>46269</v>
       </c>
       <c r="B124" t="n">
         <v>216</v>
       </c>
-      <c r="C124" s="2" t="n">
-        <v>2906000</v>
-      </c>
-      <c r="D124" s="2" t="n"/>
+      <c r="C124" s="2" t="n"/>
+      <c r="D124" s="2" t="n">
+        <v>2672000</v>
+      </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Zarafshon Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>336850572</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000607837882001</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Ijtimoiy soliq avgust 2026</t>
+          <t>Предоплата за товар по договору №78/26 от 04.09.2026</t>
         </is>
       </c>
       <c r="J124" s="2" t="n">
-        <v>80296000</v>
+        <v>232280000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="3" t="n">
-        <v>46280</v>
+        <v>46269</v>
       </c>
       <c r="B125" t="n">
         <v>217</v>
       </c>
       <c r="C125" s="2" t="n">
-        <v>2906000</v>
+        <v>9001000</v>
       </c>
       <c r="D125" s="2" t="n"/>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Mehnat Non MChJ</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>267657283</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000254733554001</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>JShDS avgust oyi uchun</t>
+          <t>Предоплата за материалы по договору №69/26</t>
         </is>
       </c>
       <c r="J125" s="2" t="n">
-        <v>77390000</v>
+        <v>223279000</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="3" t="n">
-        <v>46281</v>
+        <v>46269</v>
       </c>
       <c r="B126" t="n">
         <v>218</v>
       </c>
       <c r="C126" s="2" t="n">
-        <v>10561000</v>
+        <v>18940000</v>
       </c>
       <c r="D126" s="2" t="n"/>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Mehnat Polimer MChJ</t>
+          <t>Lazzat Oziq-ovqat Savdo AJ</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>267270449</t>
+          <t>331053414</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>20208000582882038001</t>
+          <t>20208000402896757001</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №91/26, QQS bilan</t>
+          <t>Оплата за упаковочные материалы, с/ф №9939</t>
         </is>
       </c>
       <c r="J126" s="2" t="n">
-        <v>66829000</v>
+        <v>204339000</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="3" t="n">
-        <v>46282</v>
+        <v>46272</v>
       </c>
       <c r="B127" t="n">
         <v>219</v>
       </c>
       <c r="C127" s="2" t="n"/>
       <c r="D127" s="2" t="n">
-        <v>23719000</v>
+        <v>21105000</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Nurafshon Metall MChJ</t>
+          <t>Navro'z Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>325368505</t>
+          <t>343268290</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>20208000246078378001</t>
+          <t>20208000249638040001</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №42/26, QQS 12%</t>
+          <t>Оплата по счет-фактуре №5955 за поставленный товар</t>
         </is>
       </c>
       <c r="J127" s="2" t="n">
-        <v>90548000</v>
+        <v>225444000</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="3" t="n">
-        <v>46282</v>
+        <v>46272</v>
       </c>
       <c r="B128" t="n">
         <v>220</v>
       </c>
       <c r="C128" s="2" t="n"/>
       <c r="D128" s="2" t="n">
-        <v>20337000</v>
+        <v>7166000</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Nurafshon Metall MChJ</t>
+          <t>Zarafshon Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>325368505</t>
+          <t>336850572</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>20208000246078378001</t>
+          <t>20208000607837882001</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №2308</t>
+          <t>Оплата за товар по счет-фактуре №7284 от 07.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J128" s="2" t="n">
-        <v>110885000</v>
+        <v>232610000</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="3" t="n">
-        <v>46283</v>
+        <v>46272</v>
       </c>
       <c r="B129" t="n">
         <v>221</v>
       </c>
       <c r="C129" s="2" t="n"/>
       <c r="D129" s="2" t="n">
-        <v>9464000</v>
+        <v>1834000</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Nurafshon Metall MChJ</t>
+          <t>Saodat Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>325368505</t>
+          <t>256884648</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>20208000246078378001</t>
+          <t>20208000716469607001</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №8131</t>
+          <t>Shartnoma №124/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J129" s="2" t="n">
-        <v>120349000</v>
+        <v>234444000</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="3" t="n">
-        <v>46285</v>
+        <v>46272</v>
       </c>
       <c r="B130" t="n">
         <v>222</v>
       </c>
       <c r="C130" s="2" t="n">
-        <v>33500000</v>
+        <v>6290000</v>
       </c>
       <c r="D130" s="2" t="n"/>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-5531)</t>
+          <t>Mehnat Non MChJ</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>267657283</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>16307000202482792417</t>
+          <t>20208000254733554001</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-5531 bo'yicha navbatdagi to'lov (09.2026)</t>
+          <t>Tovarlar uchun to'lov h/f №8501</t>
         </is>
       </c>
       <c r="J130" s="2" t="n">
-        <v>86849000</v>
+        <v>228154000</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="3" t="n">
-        <v>46287</v>
+        <v>46272</v>
       </c>
       <c r="B131" t="n">
         <v>223</v>
       </c>
-      <c r="C131" s="2" t="n"/>
-      <c r="D131" s="2" t="n">
-        <v>25926000</v>
-      </c>
+      <c r="C131" s="2" t="n">
+        <v>21309000</v>
+      </c>
+      <c r="D131" s="2" t="n"/>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Nihol Oziq-ovqat Savdo AJ</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>349483499</t>
+          <t>Sarbon Moliya Bank</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>20208000682636274001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Shartnoma №227/26 bo'yicha oldindan to'lov</t>
+          <t>Перечисление заработной платы за август 2026 г. согласно реестру №2327</t>
         </is>
       </c>
       <c r="J131" s="2" t="n">
-        <v>112775000</v>
+        <v>206845000</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="3" t="n">
-        <v>46287</v>
+        <v>46272</v>
       </c>
       <c r="B132" t="n">
         <v>224</v>
       </c>
-      <c r="C132" s="2" t="n"/>
-      <c r="D132" s="2" t="n">
-        <v>10073000</v>
-      </c>
+      <c r="C132" s="2" t="n">
+        <v>22893000</v>
+      </c>
+      <c r="D132" s="2" t="n"/>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Nurafshon Metall MChJ</t>
+          <t>Mehnat Non MChJ</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>325368505</t>
+          <t>267657283</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>20208000246078378001</t>
+          <t>20208000254733554001</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Shartnoma №64/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за транспортные услуги по договору №75/26</t>
         </is>
       </c>
       <c r="J132" s="2" t="n">
-        <v>122848000</v>
+        <v>183952000</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="3" t="n">
-        <v>46287</v>
+        <v>46273</v>
       </c>
       <c r="B133" t="n">
         <v>225</v>
       </c>
-      <c r="C133" s="2" t="n">
-        <v>6489000</v>
-      </c>
-      <c r="D133" s="2" t="n"/>
+      <c r="C133" s="2" t="n"/>
+      <c r="D133" s="2" t="n">
+        <v>22410000</v>
+      </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Zarafshon Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>336850572</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000607837882001</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>QQS avgust 2026 uchun</t>
+          <t>Оплата по счет-фактуре №7392 за поставленный товар</t>
         </is>
       </c>
       <c r="J133" s="2" t="n">
-        <v>116359000</v>
+        <v>206362000</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="3" t="n">
-        <v>46288</v>
+        <v>46273</v>
       </c>
       <c r="B134" t="n">
         <v>226</v>
       </c>
       <c r="C134" s="2" t="n"/>
       <c r="D134" s="2" t="n">
-        <v>47566000</v>
+        <v>15587000</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Nurafshon Metall MChJ</t>
+          <t>Zarafshon Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>325368505</t>
+          <t>336850572</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>20208000246078378001</t>
+          <t>20208000607837882001</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Shartnoma №101/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата по счет-фактуре №5106 за поставленный товар</t>
         </is>
       </c>
       <c r="J134" s="2" t="n">
-        <v>163925000</v>
+        <v>221949000</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="3" t="n">
-        <v>46288</v>
+        <v>46273</v>
       </c>
       <c r="B135" t="n">
         <v>227</v>
       </c>
       <c r="C135" s="2" t="n">
-        <v>46218000</v>
+        <v>3718000</v>
       </c>
       <c r="D135" s="2" t="n"/>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Mehnat Polimer MChJ</t>
+          <t>Durdona Qurilish MChJ</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>267270449</t>
+          <t>312569656</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>20208000582882038001</t>
+          <t>20208000417219297001</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по дог. №154/26</t>
+          <t>Арендная плата за сентябрь 2026 г. по договору №11/23</t>
         </is>
       </c>
       <c r="J135" s="2" t="n">
-        <v>117707000</v>
+        <v>218231000</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="3" t="n">
-        <v>46290</v>
+        <v>46274</v>
       </c>
       <c r="B136" t="n">
         <v>228</v>
       </c>
-      <c r="C136" s="2" t="n">
-        <v>9294000</v>
-      </c>
-      <c r="D136" s="2" t="n"/>
+      <c r="C136" s="2" t="n"/>
+      <c r="D136" s="2" t="n">
+        <v>15487000</v>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Mehnat Polimer MChJ</t>
+          <t>Chust Mebel MChJ</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>267270449</t>
+          <t>395380844</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>20208000582882038001</t>
+          <t>20208000235273440001</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartn. №89/26, QQS bilan</t>
+          <t>ОПЛАТА ЗА ТОВАР ПО СЧЕТ-ФАКТУРЕ №7540 ОТ 09.09.2026, В Т.Ч. НДС 12%</t>
         </is>
       </c>
       <c r="J136" s="2" t="n">
-        <v>108413000</v>
+        <v>233718000</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="3" t="n">
-        <v>46290</v>
+        <v>46274</v>
       </c>
       <c r="B137" t="n">
         <v>229</v>
       </c>
-      <c r="C137" s="2" t="n">
-        <v>59280000</v>
-      </c>
-      <c r="D137" s="2" t="n"/>
+      <c r="C137" s="2" t="n"/>
+      <c r="D137" s="2" t="n">
+        <v>2442000</v>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Mehnat Polimer MChJ</t>
+          <t>Zarafshon Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>267270449</t>
+          <t>336850572</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>20208000582882038001</t>
+          <t>20208000607837882001</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №4778</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №8096</t>
         </is>
       </c>
       <c r="J137" s="2" t="n">
-        <v>49133000</v>
+        <v>236160000</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="3" t="n">
-        <v>46293</v>
+        <v>46274</v>
       </c>
       <c r="B138" t="n">
         <v>230</v>
       </c>
-      <c r="C138" s="2" t="n"/>
-      <c r="D138" s="2" t="n">
-        <v>63123000</v>
-      </c>
+      <c r="C138" s="2" t="n">
+        <v>13111000</v>
+      </c>
+      <c r="D138" s="2" t="n"/>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Nihol Sut Mahsulotlari MChJ</t>
+          <t>Mehnat Non MChJ</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>308432682</t>
+          <t>267657283</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>20208000052496380001</t>
+          <t>20208000254733554001</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №6938</t>
+          <t>Предоплата за материалы по договору №104/26</t>
         </is>
       </c>
       <c r="J138" s="2" t="n">
-        <v>112256000</v>
+        <v>223049000</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="3" t="n">
-        <v>46293</v>
+        <v>46276</v>
       </c>
       <c r="B139" t="n">
         <v>231</v>
       </c>
       <c r="C139" s="2" t="n"/>
       <c r="D139" s="2" t="n">
-        <v>58738000</v>
+        <v>89682000</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Nurafshon Metall MChJ</t>
+          <t>Zarafshon Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>325368505</t>
+          <t>336850572</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>20208000246078378001</t>
+          <t>20208000607837882001</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №9985 за поставленный товар</t>
+          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГ. №247/26, НДС 12%</t>
         </is>
       </c>
       <c r="J139" s="2" t="n">
-        <v>170994000</v>
+        <v>312731000</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="3" t="n">
-        <v>46293</v>
+        <v>46276</v>
       </c>
       <c r="B140" t="n">
         <v>232</v>
       </c>
-      <c r="C140" s="2" t="n">
-        <v>2324000</v>
-      </c>
-      <c r="D140" s="2" t="n"/>
+      <c r="C140" s="2" t="n"/>
+      <c r="D140" s="2" t="n">
+        <v>13034000</v>
+      </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Zarafshon Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>336850572</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>20208000572345125001</t>
+          <t>20208000607837882001</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Оплата за электроэнергию за сентябрь 2026 г.</t>
+          <t>Оплата за товар по счет-фактуре №4439 от 11.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J140" s="2" t="n">
-        <v>168670000</v>
+        <v>325765000</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="3" t="n">
-        <v>46293</v>
+        <v>46276</v>
       </c>
       <c r="B141" t="n">
         <v>233</v>
       </c>
-      <c r="C141" s="2" t="n">
-        <v>4025000</v>
-      </c>
-      <c r="D141" s="2" t="n"/>
+      <c r="C141" s="2" t="n"/>
+      <c r="D141" s="2" t="n">
+        <v>11499000</v>
+      </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Mehnat Polimer MChJ</t>
+          <t>Lazzat Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>267270449</t>
+          <t>236565783</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>20208000582882038001</t>
+          <t>20208000607229325001</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -5846,151 +5851,1506 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №259/26</t>
+          <t>Оплата по счет-фактуре №7736 за поставленный товар</t>
         </is>
       </c>
       <c r="J141" s="2" t="n">
-        <v>164645000</v>
+        <v>337264000</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="3" t="n">
-        <v>46294</v>
+        <v>46279</v>
       </c>
       <c r="B142" t="n">
         <v>234</v>
       </c>
-      <c r="C142" s="2" t="n">
-        <v>28003000</v>
-      </c>
-      <c r="D142" s="2" t="n"/>
+      <c r="C142" s="2" t="n"/>
+      <c r="D142" s="2" t="n">
+        <v>27069000</v>
+      </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Mehnat Polimer MChJ</t>
+          <t>Chust Mebel MChJ</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>267270449</t>
+          <t>395380844</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>20208000582882038001</t>
+          <t>20208000235273440001</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №189/26</t>
+          <t>Оплата по с/ф №6686 за поставленный товар</t>
         </is>
       </c>
       <c r="J142" s="2" t="n">
-        <v>136642000</v>
+        <v>364333000</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="3" t="n">
-        <v>46295</v>
+        <v>46279</v>
       </c>
       <c r="B143" t="n">
         <v>235</v>
       </c>
-      <c r="C143" s="2" t="n"/>
-      <c r="D143" s="2" t="n">
-        <v>15358000</v>
-      </c>
+      <c r="C143" s="2" t="n">
+        <v>9812000</v>
+      </c>
+      <c r="D143" s="2" t="n"/>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Nurafshon Metall MChJ</t>
+          <t>Lazzat Oziq-ovqat Savdo AJ</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>325368505</t>
+          <t>331053414</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>20208000246078378001</t>
+          <t>20208000402896757001</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №3989 от 30.09.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за транспортные услуги по договору №101/26</t>
         </is>
       </c>
       <c r="J143" s="2" t="n">
-        <v>152000000</v>
+        <v>354521000</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="3" t="n">
-        <v>46295</v>
+        <v>46280</v>
       </c>
       <c r="B144" t="n">
         <v>236</v>
       </c>
       <c r="C144" s="2" t="n">
-        <v>300000</v>
+        <v>2906000</v>
       </c>
       <c r="D144" s="2" t="n"/>
       <c r="E144" t="inlineStr">
         <is>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>201122905</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>23402000300100001010</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>00014</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>Уплата социального налога за август</t>
+        </is>
+      </c>
+      <c r="J144" s="2" t="n">
+        <v>351615000</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="3" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B145" t="n">
+        <v>237</v>
+      </c>
+      <c r="C145" s="2" t="n">
+        <v>2906000</v>
+      </c>
+      <c r="D145" s="2" t="n"/>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>201122905</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>23402000300100001010</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>00014</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>НДФЛ за август 2026</t>
+        </is>
+      </c>
+      <c r="J145" s="2" t="n">
+        <v>348709000</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="3" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B146" t="n">
+        <v>238</v>
+      </c>
+      <c r="C146" s="2" t="n">
+        <v>19260000</v>
+      </c>
+      <c r="D146" s="2" t="n"/>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Mehnat Non MChJ</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>267657283</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>20208000254733554001</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №148/26</t>
+        </is>
+      </c>
+      <c r="J146" s="2" t="n">
+        <v>329449000</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="3" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B147" t="n">
+        <v>239</v>
+      </c>
+      <c r="C147" s="2" t="n"/>
+      <c r="D147" s="2" t="n">
+        <v>40816000</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Saodat Un Mahsulotlari MChJ</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>256884648</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>20208000716469607001</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>Оплата за продукцию по договору №245/26, НДС 12%</t>
+        </is>
+      </c>
+      <c r="J147" s="2" t="n">
+        <v>370265000</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="3" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B148" t="n">
+        <v>240</v>
+      </c>
+      <c r="C148" s="2" t="n"/>
+      <c r="D148" s="2" t="n">
+        <v>15119000</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Zarafshon Avto Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>336850572</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>20208000607837882001</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>Оплата по счет-фактуре №740 за поставленный товар</t>
+        </is>
+      </c>
+      <c r="J148" s="2" t="n">
+        <v>385384000</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="3" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B149" t="n">
+        <v>241</v>
+      </c>
+      <c r="C149" s="2" t="n"/>
+      <c r="D149" s="2" t="n">
+        <v>3401000</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Zarafshon Avto Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>336850572</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>20208000607837882001</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>Оплата по с/ф №1889 за поставленный товар</t>
+        </is>
+      </c>
+      <c r="J149" s="2" t="n">
+        <v>388785000</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="3" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B150" t="n">
+        <v>242</v>
+      </c>
+      <c r="C150" s="2" t="n"/>
+      <c r="D150" s="2" t="n">
+        <v>7953000</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Saodat Un Mahsulotlari MChJ</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>256884648</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>20208000716469607001</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>Предоплата за товар по договору №272/26 от 18.09.2026</t>
+        </is>
+      </c>
+      <c r="J150" s="2" t="n">
+        <v>396738000</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="3" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B151" t="n">
+        <v>243</v>
+      </c>
+      <c r="C151" s="2" t="n"/>
+      <c r="D151" s="2" t="n">
+        <v>2858000</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Andijon Avto Savdo XK</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>237378303</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>20208000073551515001</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>00962</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>Предоплата за товар по дог. №90/26 от 18.09.2026</t>
+        </is>
+      </c>
+      <c r="J151" s="2" t="n">
+        <v>399596000</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="3" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B152" t="n">
+        <v>244</v>
+      </c>
+      <c r="C152" s="2" t="n">
+        <v>16814000</v>
+      </c>
+      <c r="D152" s="2" t="n"/>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Lazzat Oziq-ovqat Savdo AJ</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>331053414</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>20208000402896757001</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>00962</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>Оплата за товары согласно с/ф №3507</t>
+        </is>
+      </c>
+      <c r="J152" s="2" t="n">
+        <v>382782000</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="3" t="n">
+        <v>46285</v>
+      </c>
+      <c r="B153" t="n">
+        <v>245</v>
+      </c>
+      <c r="C153" s="2" t="n">
+        <v>33500000</v>
+      </c>
+      <c r="D153" s="2" t="n"/>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-5531)</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>16307000202482792417</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>00962</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>Kredit shartnomasi L-2025-5531 bo'yicha navbatdagi to'lov (09.2026)</t>
+        </is>
+      </c>
+      <c r="J153" s="2" t="n">
+        <v>349282000</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="3" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B154" t="n">
+        <v>246</v>
+      </c>
+      <c r="C154" s="2" t="n"/>
+      <c r="D154" s="2" t="n">
+        <v>13500000</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Saodat Un Mahsulotlari MChJ</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>256884648</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>20208000716469607001</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>Предоплата за товар по договору №239/26 от 21.09.2026</t>
+        </is>
+      </c>
+      <c r="J154" s="2" t="n">
+        <v>362782000</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="3" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B155" t="n">
+        <v>247</v>
+      </c>
+      <c r="C155" s="2" t="n"/>
+      <c r="D155" s="2" t="n">
+        <v>4405000</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Zarafshon Avto Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>336850572</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>20208000607837882001</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Оплата за товар по счет-фактуре №5865 от 21.09.2026, в т.ч. НДС 12%</t>
+        </is>
+      </c>
+      <c r="J155" s="2" t="n">
+        <v>367187000</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="3" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B156" t="n">
+        <v>248</v>
+      </c>
+      <c r="C156" s="2" t="n"/>
+      <c r="D156" s="2" t="n">
+        <v>2947000</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Zarafshon Avto Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>336850572</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>20208000607837882001</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>Предоплата за товар по дог. №47/26 от 21.09.2026</t>
+        </is>
+      </c>
+      <c r="J156" s="2" t="n">
+        <v>370134000</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="3" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B157" t="n">
+        <v>249</v>
+      </c>
+      <c r="C157" s="2" t="n"/>
+      <c r="D157" s="2" t="n">
+        <v>2683000</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Zarafshon Avto Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>336850572</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>20208000607837882001</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Предоплата за товар по договору №184/26 от 21.09.2026</t>
+        </is>
+      </c>
+      <c r="J157" s="2" t="n">
+        <v>372817000</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="3" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B158" t="n">
+        <v>250</v>
+      </c>
+      <c r="C158" s="2" t="n">
+        <v>5955000</v>
+      </c>
+      <c r="D158" s="2" t="n"/>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Lazzat Oziq-ovqat Savdo AJ</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>331053414</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>20208000402896757001</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>00962</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Оплата за упаковочные материалы, с/ф №9146</t>
+        </is>
+      </c>
+      <c r="J158" s="2" t="n">
+        <v>366862000</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="3" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B159" t="n">
+        <v>251</v>
+      </c>
+      <c r="C159" s="2" t="n">
+        <v>28369000</v>
+      </c>
+      <c r="D159" s="2" t="n"/>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Mehnat Non MChJ</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>267657283</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>20208000254733554001</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>Предоплата за материалы по дог. №127/26</t>
+        </is>
+      </c>
+      <c r="J159" s="2" t="n">
+        <v>338493000</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="3" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B160" t="n">
+        <v>252</v>
+      </c>
+      <c r="C160" s="2" t="n">
+        <v>33071000</v>
+      </c>
+      <c r="D160" s="2" t="n"/>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Mehnat Non MChJ</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>267657283</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>20208000254733554001</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Оплата за товары согласно с/ф №2168</t>
+        </is>
+      </c>
+      <c r="J160" s="2" t="n">
+        <v>305422000</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="3" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B161" t="n">
+        <v>253</v>
+      </c>
+      <c r="C161" s="2" t="n"/>
+      <c r="D161" s="2" t="n">
+        <v>3864000</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Zarafshon Avto Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>336850572</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>20208000607837882001</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Предоплата за товар по договору №286/26 от 22.09.2026</t>
+        </is>
+      </c>
+      <c r="J161" s="2" t="n">
+        <v>309286000</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="3" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B162" t="n">
+        <v>254</v>
+      </c>
+      <c r="C162" s="2" t="n">
+        <v>53494000</v>
+      </c>
+      <c r="D162" s="2" t="n"/>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Nukus Mebel MChJ</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>328573767</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>20208000514928282001</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Предоплата за материалы по договору №267/26</t>
+        </is>
+      </c>
+      <c r="J162" s="2" t="n">
+        <v>255792000</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="3" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B163" t="n">
+        <v>255</v>
+      </c>
+      <c r="C163" s="2" t="n"/>
+      <c r="D163" s="2" t="n">
+        <v>3658000</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Navro'z Dori-Darmon MChJ</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>343268290</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>20208000249638040001</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Yetkazilgan tovar uchun to'lov h/f №5058</t>
+        </is>
+      </c>
+      <c r="J163" s="2" t="n">
+        <v>259450000</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="3" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B164" t="n">
+        <v>256</v>
+      </c>
+      <c r="C164" s="2" t="n">
+        <v>2324000</v>
+      </c>
+      <c r="D164" s="2" t="n"/>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Hududiy elektr tarmoqlari AJ</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>200933985</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>20208000092438345001</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>00962</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Elektr energiyasi uchun to'lov</t>
+        </is>
+      </c>
+      <c r="J164" s="2" t="n">
+        <v>257126000</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="3" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B165" t="n">
+        <v>257</v>
+      </c>
+      <c r="C165" s="2" t="n">
+        <v>6195000</v>
+      </c>
+      <c r="D165" s="2" t="n"/>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>201122905</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>23402000300100001010</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>00014</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>QQS avgust 2026 uchun</t>
+        </is>
+      </c>
+      <c r="J165" s="2" t="n">
+        <v>250931000</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="3" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B166" t="n">
+        <v>258</v>
+      </c>
+      <c r="C166" s="2" t="n">
+        <v>9826000</v>
+      </c>
+      <c r="D166" s="2" t="n"/>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Lazzat Oziq-ovqat Savdo AJ</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>331053414</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>20208000402896757001</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>00962</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Оплата за товары соласно счет-фактуре №9626</t>
+        </is>
+      </c>
+      <c r="J166" s="2" t="n">
+        <v>241105000</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="3" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B167" t="n">
+        <v>259</v>
+      </c>
+      <c r="C167" s="2" t="n"/>
+      <c r="D167" s="2" t="n">
+        <v>20185000</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Kattaqo'rg'on Dori-Darmon MChJ</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>348349936</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>20208000263627433001</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>00962</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Предоплата за товар по договору №192/26 от 24.09.2026</t>
+        </is>
+      </c>
+      <c r="J167" s="2" t="n">
+        <v>261290000</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="3" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B168" t="n">
+        <v>260</v>
+      </c>
+      <c r="C168" s="2" t="n"/>
+      <c r="D168" s="2" t="n">
+        <v>1936000</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Saodat Un Mahsulotlari MChJ</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>256884648</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>20208000716469607001</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>Mahsulot uchun to'lov, shartnoma №35/26, QQS 12%</t>
+        </is>
+      </c>
+      <c r="J168" s="2" t="n">
+        <v>263226000</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="3" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B169" t="n">
+        <v>261</v>
+      </c>
+      <c r="C169" s="2" t="n">
+        <v>6497000</v>
+      </c>
+      <c r="D169" s="2" t="n"/>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Mehnat Non MChJ</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>267657283</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>20208000254733554001</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Оплата за упаковочные материалы, с/ф №7266</t>
+        </is>
+      </c>
+      <c r="J169" s="2" t="n">
+        <v>256729000</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="3" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B170" t="n">
+        <v>262</v>
+      </c>
+      <c r="C170" s="2" t="n">
+        <v>75710000</v>
+      </c>
+      <c r="D170" s="2" t="n"/>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Mehnat Non MChJ</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>267657283</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>20208000254733554001</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Оплата за упаковочные материалы, с/ф №6818</t>
+        </is>
+      </c>
+      <c r="J170" s="2" t="n">
+        <v>181019000</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B171" t="n">
+        <v>263</v>
+      </c>
+      <c r="C171" s="2" t="n"/>
+      <c r="D171" s="2" t="n">
+        <v>14437000</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Lazzat Mehmonxona MChJ</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>236565783</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>20208000607229325001</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>01089</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>Оплата по с/ф №9943 за поставленный товар</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="n">
+        <v>195456000</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B172" t="n">
+        <v>264</v>
+      </c>
+      <c r="C172" s="2" t="n"/>
+      <c r="D172" s="2" t="n">
+        <v>4943000</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Zarafshon Avto Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>336850572</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>20208000607837882001</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>Оплата за товар по счет-фактуре №8480 от 28.09.2026, в т.ч. НДС 12%</t>
+        </is>
+      </c>
+      <c r="J172" s="2" t="n">
+        <v>200399000</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B173" t="n">
+        <v>265</v>
+      </c>
+      <c r="C173" s="2" t="n"/>
+      <c r="D173" s="2" t="n">
+        <v>3201000</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Navro'z Dori-Darmon MChJ</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>343268290</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>20208000249638040001</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>Оплата по счет-фактуре №1295 за поставленный товар</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="n">
+        <v>203600000</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B174" t="n">
+        <v>266</v>
+      </c>
+      <c r="C174" s="2" t="n">
+        <v>61277000</v>
+      </c>
+      <c r="D174" s="2" t="n"/>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Tong Savdo AJ</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>281252850</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>20208000537007953001</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>Оплата за товары согласно счет-фактуре №1595</t>
+        </is>
+      </c>
+      <c r="J174" s="2" t="n">
+        <v>142323000</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="3" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B175" t="n">
+        <v>267</v>
+      </c>
+      <c r="C175" s="2" t="n"/>
+      <c r="D175" s="2" t="n">
+        <v>29255000</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Kattaqo'rg'on Dori-Darmon MChJ</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>348349936</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>20208000263627433001</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>00962</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>Оплата за товар по счет-фактуре №4074 от 30.09.2026, в т.ч.НДС 12%</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="n">
+        <v>171578000</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="3" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B176" t="n">
+        <v>268</v>
+      </c>
+      <c r="C176" s="2" t="n"/>
+      <c r="D176" s="2" t="n">
+        <v>2975000</v>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Saodat Un Mahsulotlari MChJ</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>256884648</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>20208000716469607001</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>Tovar uchun to'lov, hisob-faktura №8033 30.09.2026, QQS bilan</t>
+        </is>
+      </c>
+      <c r="J176" s="2" t="n">
+        <v>174553000</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="3" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B177" t="n">
+        <v>269</v>
+      </c>
+      <c r="C177" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D177" s="2" t="n"/>
+      <c r="E177" t="inlineStr">
+        <is>
           <t>Sarbon Moliya Bank</t>
         </is>
       </c>
-      <c r="G144" t="inlineStr">
+      <c r="G177" t="inlineStr">
         <is>
           <t>45994000900000001001</t>
         </is>
       </c>
-      <c r="H144" t="inlineStr">
+      <c r="H177" t="inlineStr">
         <is>
           <t>00962</t>
         </is>
       </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>BANK XIZMATI UCHUN KOMISSIYA</t>
-        </is>
-      </c>
-      <c r="J144" s="2" t="n">
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>Комиссия за перевод</t>
+        </is>
+      </c>
+      <c r="J177" s="2" t="n">
+        <v>174253000</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="3" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B178" t="n">
+        <v>270</v>
+      </c>
+      <c r="C178" s="2" t="n">
+        <v>22553000</v>
+      </c>
+      <c r="D178" s="2" t="n"/>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Lazzat Oziq-ovqat Savdo AJ</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>331053414</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>20208000402896757001</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>00962</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>Оплата за транспортные услуги по дог. №179/26</t>
+        </is>
+      </c>
+      <c r="J178" s="2" t="n">
         <v>151700000</v>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
+    <row r="179">
+      <c r="A179" t="inlineStr">
         <is>
           <t>Итого обороты:</t>
         </is>
       </c>
-      <c r="C145" s="4" t="n">
-        <v>1502606000</v>
-      </c>
-      <c r="D145" s="4" t="n">
-        <v>1478206000</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
+      <c r="C179" s="4" t="n">
+        <v>1482267000</v>
+      </c>
+      <c r="D179" s="4" t="n">
+        <v>1457867000</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
         <is>
           <t>Исходящий остаток на 30.09.2026:</t>
         </is>
       </c>
-      <c r="C146" s="4" t="n">
+      <c r="C180" s="4" t="n">
         <v>151700000</v>
       </c>
-      <c r="D146" s="4" t="n"/>
+      <c r="D180" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
